--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,13 +158,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,29 +775,29 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>569.8</v>
-      </c>
-      <c r="D4" s="11" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -815,13 +806,13 @@
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>4.3</v>
@@ -829,23 +820,23 @@
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>10.3</v>
+      <c r="W4" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>12.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -860,22 +851,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -889,10 +886,10 @@
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>35.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>21.6</v>
+        <v>0.4</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -901,19 +898,19 @@
         <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.7</v>
+        <v>31.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>41</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.2</v>
@@ -925,10 +922,10 @@
         <v>8.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>201.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.1</v>
+        <v>80.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -943,18 +940,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="n">
-        <v>31.9</v>
+      <c r="F6" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -963,25 +966,25 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>12.2</v>
+      <c r="L6" s="13" t="n">
+        <v>488.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -990,7 +993,7 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>14.4</v>
@@ -1002,10 +1005,10 @@
         <v>28.9</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>16.3</v>
@@ -1027,22 +1030,22 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>583.6</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1051,7 +1054,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1060,16 +1063,16 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
+        <v>39.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>13.8</v>
@@ -1090,10 +1093,10 @@
         <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.3</v>
@@ -1112,39 +1115,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>34.4</v>
-      </c>
+        <v>25.1</v>
+      </c>
+      <c r="D8" s="9" t="n"/>
       <c r="E8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>22.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>22.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>27.2</v>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>36.5</v>
+        <v>0.8</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1156,7 +1157,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1165,13 +1166,13 @@
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>22.1</v>
@@ -1193,19 +1194,27 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="10" t="n"/>
+        <v>2656.2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>106.4</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="n">
         <v>44.2</v>
       </c>
@@ -1213,48 +1222,48 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n">
-        <v>28.8</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183.8</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>165</v>
+        <v>1685</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>71.8</v>
+        <v>24.8</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.1</v>
+        <v>24.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>38.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>106.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1270,15 +1279,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>534.4</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>22.3</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1291,24 +1300,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>13.7</v>
+        <v>2.7</v>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="n">
-        <v>13.4</v>
+      <c r="L10" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.2</v>
+        <v>32.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>36.6</v>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
@@ -1316,28 +1323,28 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>13.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>38.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>184.1</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>150.2</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1353,25 +1360,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
+        <v>422.9</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>23.7</v>
+        <v>42.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
+        <v>41.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
@@ -1383,14 +1390,18 @@
       <c r="M11" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>0.2</v>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+8
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
@@ -1400,22 +1411,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>81</v>
+        <v>31.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>47</v>
+        <v>424</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1431,26 +1442,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 6
-</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>31.6</v>
+      <c r="C12" s="3" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>11.9</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F12" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>19.9</v>
+      <c r="G12" s="13" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.1</v>
@@ -1459,7 +1467,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1468,7 +1476,7 @@
         <v>6.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
@@ -1476,35 +1484,37 @@
       <c r="P12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
+      <c r="Q12" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>29.2</v>
+        <v>92.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+76
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1520,21 +1530,21 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>601.3</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E13" s="11" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G13" s="11" t="n">
+      <c r="F13" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1553,19 +1563,19 @@
         <v>12.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.3</v>
+      <c r="R13" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1574,19 +1584,19 @@
         <v>13.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>28.7</v>
+        <v>49.6</v>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>87.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1605,19 +1615,19 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="D14" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1627,43 +1637,43 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1.8</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>9.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="R14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>27</v>
+        <v>41.2</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>9.199999999999999</v>
@@ -1688,16 +1698,16 @@
       <c r="C15" s="3" t="n">
         <v>552.4</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>31.2</v>
+      <c r="D15" s="3" t="n">
+        <v>34.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>15</v>
+        <v>79.5</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1710,16 +1720,16 @@
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>48</v>
@@ -1730,11 +1740,11 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>14.3</v>
+      <c r="R15" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>15.4</v>
@@ -1743,7 +1753,7 @@
         <v>38</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>14</v>
@@ -1755,7 +1765,7 @@
         <v>23.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1771,16 +1781,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9572.1</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>158.7</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>118.2</v>
+        <v>2577.7</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>8.1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1789,29 +1799,39 @@
         <v>10.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
+14
+</t>
+        </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>822.3</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>2121.5</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>54.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>23.6</v>
@@ -1820,23 +1840,29 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>820.6</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="n">
         <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>148.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.5</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1852,74 +1878,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G17" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>30.9</v>
+      <c r="P17" s="13" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>60.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>7.3</v>
+        <v>72.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>96.3</v>
+        <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.1</v>
+        <v>212.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,63 +1960,62 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>552.1</v>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+2
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 7
-</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n"/>
+        <v>34.9</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1.1</v>
+        <v>32.9</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>37.6</v>
+        <v>166.9</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
@@ -2005,7 +2030,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2020,23 +2045,27 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>326.4</v>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+2975
+</t>
+        </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.4</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.8</v>
@@ -2045,7 +2074,7 @@
         <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>13.5</v>
@@ -2053,19 +2082,17 @@
       <c r="M19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R19" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2075,19 +2102,19 @@
         <v>12.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>20.4</v>
+        <v>4.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2103,15 +2130,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D20" s="13" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.3</v>
+        <v>12.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2120,34 +2152,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32</v>
+        <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2156,15 +2188,17 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41.4</v>
+        <v>4.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Y20" s="3" t="n">
         <v>32</v>
       </c>
@@ -2183,59 +2217,61 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F21" s="3" t="n">
+        <v>542.2</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>5.5</v>
+      <c r="G21" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>23.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>25.6</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>492</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>2.6</v>
+        <v>12.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>26.3</v>
@@ -2250,7 +2286,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2266,16 +2302,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>516.3</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>3.6</v>
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>22.5</v>
+      <c r="F22" s="11" t="n">
+        <v>43.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2284,31 +2320,31 @@
         <v>13.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J22" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>51</v>
+        <v>21.1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>30.7</v>
+        <v>22.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>4.5</v>
@@ -2317,19 +2353,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
+        <v>14.9</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>98.2</v>
+        <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2348,63 +2384,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>117.1</v>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="10" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>11.6</v>
+        <v>86.8</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44255
+82947
+</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="K23" s="3" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>23</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>31.3</v>
+        <v>5.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.5</v>
+        <v>30.5</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>68.8</v>
@@ -2413,9 +2453,11 @@
         <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>192.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2430,51 +2472,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5032.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>5026.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="11" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>17.4</v>
+      <c r="E24" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>78.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>50.3</v>
+        <v>5.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R24" s="8" t="n">
+      <c r="Q24" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2483,11 +2525,11 @@
       <c r="T24" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U24" s="8" t="n">
+      <c r="U24" s="13" t="n">
         <v>87.2</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
@@ -2496,10 +2538,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2515,68 +2557,77 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>31.9</v>
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>14.9</v>
+        <v>4.2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>400.8</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>14.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n">
-        <v>88.8</v>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+2
+</t>
+        </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>45.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2595,39 +2646,41 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>44.8</v>
+      <c r="E26" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n">
-        <v>10.9</v>
+        <v>72.3</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>8.9</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2639,25 +2692,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U26" s="8" t="n">
-        <v>2823.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>4.8</v>
+      <c r="U26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V26" s="13" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W26" s="13" t="n">
+        <v>49.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2674,30 +2727,32 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
+        <v>5.1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>23.3</v>
+        <v>28.58</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>681.6</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2705,13 +2760,13 @@
         <v>10.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>98.5</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1322</v>
+        <v>528</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>29.3</v>
@@ -2720,28 +2775,32 @@
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>28.2</v>
+        <v>3.4</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>44.3</v>
+        <v>4.2</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>20.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2759,74 +2818,78 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>23.5</v>
+      <c r="D28" s="3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J28" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>47</v>
+        <v>428</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>22.5</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7.2</v>
+        <v>13.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>20.8</v>
+        <v>126.5</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2842,31 +2905,31 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>0.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>34.4</v>
+        <v>3.4</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2875,10 +2938,10 @@
         <v>10.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>41.3</v>
+        <v>4.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2886,16 +2949,18 @@
       <c r="Q29" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>9.4</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>43.4</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>27.7</v>
       </c>
@@ -2923,73 +2988,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>29.3</v>
+      <c r="F30" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.9</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42</v>
+        <v>42.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>18.6</v>
+        <v>28.3</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -3006,31 +3071,31 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>18</v>
+      <c r="E31" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>18.4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>522.4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>18.9</v>
+      <c r="K31" s="13" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3044,21 +3109,19 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>14.2</v>
+      <c r="P31" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R31" s="13" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
@@ -3072,7 +3135,7 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3090,36 +3153,32 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F32" s="3" t="n">
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>23.2</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.8</v>
@@ -3137,27 +3196,27 @@
         <v>4.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T32" s="3" t="n"/>
+        <v>4.7</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>42.4</v>
+        <v>424.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>24.6</v>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3171,14 +3230,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10.6</v>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="11" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.2</v>
@@ -3187,58 +3244,58 @@
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15.8</v>
+        <v>35.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141.8</v>
+        <v>4.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>10.2</v>
+      <c r="R33" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S33" s="13" t="n">
+        <v>6.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>44.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3257,13 +3314,13 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="D34" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3273,7 +3330,7 @@
         <v>1.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3282,10 +3339,10 @@
         <v>6</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>41.2</v>
+        <v>17.2</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.8</v>
@@ -3297,13 +3354,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>2.1</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>30.3</v>
@@ -3318,13 +3375,17 @@
         <v>12.7</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>5</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+178
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3340,28 +3401,28 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>23.2</v>
+        <v>433.9</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>32.9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>19.1</v>
+        <v>12.4</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>14.2</v>
@@ -3370,14 +3431,16 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N35" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>19</v>
@@ -3389,26 +3452,24 @@
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>10.8</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3423,18 +3484,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>222.2</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E36" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="E36" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3444,10 +3505,10 @@
         <v>4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>44.2</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3455,14 +3516,12 @@
       <c r="M36" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>19.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>30.8</v>
@@ -3471,25 +3530,25 @@
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.2</v>
+        <v>21.6</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3505,57 +3564,53 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>222.2</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>11.1</v>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>11.2</v>
+        <v>42.4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>821.9</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>240.2</v>
+        <v>20.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>389.8</v>
+        <v>59.8</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>4.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>124.9</v>
+        <v>34.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>3.4</v>
@@ -3564,15 +3619,17 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>183.1</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>96.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3589,26 +3646,26 @@
       <c r="C38" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="10" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>10.3</v>
+      <c r="F38" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>55.8</v>
+        <v>5.8</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>301</v>
+      <c r="J38" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>36.1</v>
@@ -3617,43 +3674,43 @@
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>13.2</v>
+        <v>53.2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>4.7</v>
+        <v>47.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>14.5</v>
+        <v>59.8</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R38" s="13" t="n">
+        <v>48.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>151</v>
+        <v>11.6</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3672,39 +3729,41 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.1</v>
+        <v>5444.4</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>29.2</v>
+        <v>30.35</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>13.8</v>
+        <v>1.8</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>21.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>12.1</v>
+        <v>6.5</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>6000.4</v>
+      <c r="M39" s="3" t="n">
+        <v>40.6</v>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3719,25 +3778,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>20.3</v>
+        <v>0.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>29.4</v>
+        <v>2.4</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W39" s="8" t="n">
-        <v>15</v>
+      <c r="W39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3753,43 +3812,41 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D40" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="12" t="n">
         <v>21.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>51.2</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="K40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.4</v>
+        <v>94.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3797,14 +3854,14 @@
       <c r="Q40" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="R40" s="8" t="n">
-        <v>15</v>
+      <c r="R40" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>822.4</v>
+        <v>22.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3816,13 +3873,13 @@
         <v>14.7</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3838,76 +3895,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E41" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>11.2</v>
+        <v>2.7</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>9.5</v>
+        <v>23.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>52</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>19.5</v>
+        <v>197.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>32.6</v>
+        <v>2.6</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>828.9</v>
+        <v>28.9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>223.6</v>
+        <v>16.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3922,77 +3979,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G42" s="11" t="n">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+4811
+</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>53</v>
+      <c r="H42" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>18.3</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+      <c r="K42" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>11.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>13.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.1</v>
+        <v>45.5</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>165.5</v>
+        <v>16.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4008,76 +4069,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G43" s="11" t="n">
+      <c r="E43" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>9.5</v>
+        <v>98.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>58</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>76.2</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n">
-        <v>4.2</v>
+        <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>24.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>45.1</v>
+        <v>19.9</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
+      </c>
+      <c r="X43" s="13" t="n">
+        <v>41.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>25.3</v>
+        <v>285.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.8</v>
+        <v>16.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4093,76 +4152,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
+        <v>23.9</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F44" s="11" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G44" s="8" t="n">
-        <v>14.9</v>
+      <c r="G44" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>19.7</v>
+        <v>5.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.4</v>
+        <v>581.5</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>7.8</v>
+      <c r="R44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>89.8</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>1.4</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>8.4</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4178,76 +4237,78 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D45" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>22.9</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="G45" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.9</v>
+        <v>119.1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>356</v>
+        <v>6.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9</v>
+        <v>90.8</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>181.1</v>
+        <v>16.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>119.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>0.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>18.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>91.2</v>
+        <v>22.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>881.8</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>72.2</v>
+        <v>52.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>75.2</v>
+        <v>21.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>186.5</v>
+        <v>14.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>184.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>19.6</v>
+        <v>2.2</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+11
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4263,70 +4324,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>22.8</v>
+        <v>232.2</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>232.1</v>
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>35</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
+        <v>524.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>26.5</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="R46" s="13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>30.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>24.8</v>
+        <v>751.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>14.4</v>
+        <v>18.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>10.8</v>
+        <v>64.8</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>19.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,6 +49,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,22 +152,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,69 +796,59 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D4" s="12" t="n">
+        <v>1569.8</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n">
-        <v>2.8</v>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="14" t="n">
+        <v>72.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>13.2</v>
+      <c r="Q4" s="14" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -851,33 +862,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2.8</v>
+      <c r="C5" s="3" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>12.9</v>
+        <v>44.2</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.8</v>
@@ -885,47 +892,45 @@
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>35.5</v>
+      <c r="M5" s="14" t="n">
+        <v>65.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R5" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>14.2</v>
+        <v>5.7</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="14" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>10.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>8.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>21.2</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>80.8</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,24 +945,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="C6" s="3" t="n">
+        <v>1504.8</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="F6" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>2062.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -966,55 +967,53 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>488.7</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>8.4</v>
+        <v>16</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>89.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="14" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="14" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42.4</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16.3</v>
+        <v>201.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>3.3</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,76 +1029,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="D7" s="12" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I7" s="14" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>46.1</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>54.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R7" s="14" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>51.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="14" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>12.2</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.3</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,37 +1112,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>91</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>26.5</v>
+        <v>236.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1153,32 +1150,32 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="14" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>7.9</v>
+      <c r="S8" s="14" t="n">
+        <v>71</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U8" s="14" t="n">
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>1.7</v>
+        <v>45.1</v>
+      </c>
+      <c r="W8" s="14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X8" s="14" t="n">
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>22.1</v>
+        <v>86.7</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>34.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,76 +1191,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2656.2</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>106.4</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2262
-411464141
-</t>
-        </is>
+        <v>2636</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.2</v>
+        <v>1644.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M9" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>2.8</v>
+        <v>258.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>949.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1685</v>
+        <v>1169</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
+        <v>71.8</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>127.7</v>
+      </c>
       <c r="T9" s="3" t="n">
-        <v>55.9</v>
+        <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.1</v>
+        <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>139.7</v>
+        <v>1139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.6</v>
+        <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>38.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>16.2</v>
+        <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90.2</v>
+        <v>1120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1279,72 +1274,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="13" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="13" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="14" t="n">
+        <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>32.6</v>
+        <v>16.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="P10" s="3" t="n"/>
+        <v>236.6</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>99.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U10" s="14" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W10" s="13" t="n">
-        <v>38.2</v>
+      <c r="V10" s="14" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0.8</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>184.1</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>11.2</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1360,75 +1357,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>422.9</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>42.1</v>
+        <v>1427.8</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.1</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q11" s="14" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="14" t="n">
+        <v>148.9</v>
+      </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="U11" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1443,78 +1428,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>206.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>31.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6.8</v>
+        <v>16.2</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-76
-</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="W12" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="X12" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1530,75 +1511,75 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E13" s="12" t="n">
+        <v>1601.3</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="F13" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G13" s="13" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>11.8</v>
+      <c r="H13" s="14" t="n">
+        <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="14" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>11.7</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>1249</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q13" s="14" t="n">
         <v>33.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="V13" s="13" t="n">
-        <v>87.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="U13" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>28.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="X13" s="14" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>7.1</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>1265.4</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1613,22 +1594,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E14" s="12" t="n">
+        <v>1488</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G14" s="12" t="n">
+      <c r="F14" s="13" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>11.4</v>
+      <c r="H14" s="14" t="n">
+        <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8.1</v>
@@ -1637,51 +1618,45 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="P14" s="14" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="14" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>4.4</v>
+        <v>161.1</v>
+      </c>
+      <c r="U14" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>431.2</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1696,76 +1671,68 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.4</v>
+        <v>1832.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="14" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="14" t="n">
         <v>16.5</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.8</v>
+        <v>92.8</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>22.1</v>
-      </c>
+        <v>115.4</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>23.4</v>
+        <v>123.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1781,88 +1748,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2577.7</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>82.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1291.6</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>2726.8</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>18.3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.2</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>35.3</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-14
-</t>
-        </is>
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>189.9</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2952.9</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>2121.5</v>
+        <v>2212</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>54.7</v>
+        <v>1154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.6</v>
+        <v>1083.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>820.6</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-7918949
-</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>1131</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>48.3</v>
+        <v>148.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>148.8</v>
+        <v>11245.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>19.1</v>
+        <v>1124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1878,75 +1831,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>2.6</v>
+        <v>315.4</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>6.8</v>
+        <v>16</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.7</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N17" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="Q17" s="13" t="n">
-        <v>60.9</v>
+        <v>942.5</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>72.3</v>
+        <v>4.7</v>
+      </c>
+      <c r="S17" s="14" t="n">
+        <v>87.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
+        <v>37.6</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>212.1</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>44.9</v>
-      </c>
+        <v>229.2</v>
+      </c>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1960,77 +1909,73 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
-2
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="3" t="n">
-        <v>2.5</v>
+      <c r="C18" s="3" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>5.9</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q18" s="14" t="n">
+        <v>911.1</v>
+      </c>
+      <c r="R18" s="14" t="n">
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>14.4</v>
+        <v>115.5</v>
+      </c>
+      <c r="U18" s="14" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="14" t="n">
+        <v>184.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2045,49 +1990,43 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-2975
-</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="C19" s="3" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F19" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="13" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" s="14" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>60.8</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
@@ -2096,27 +2035,27 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>96.2</v>
-      </c>
+        <v>112.8</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr"/>
       <c r="W19" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2130,56 +2069,51 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.3</v>
+      <c r="C20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr"/>
+      <c r="E20" s="14" t="n">
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="14" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L20" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L20" s="14" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>11.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5</v>
+        <v>522</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>10.6</v>
+      <c r="R20" s="14" t="n">
+        <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2188,21 +2122,23 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>12.4</v>
+        <v>29.8</v>
+      </c>
+      <c r="V20" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>182.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2219,43 +2155,41 @@
       <c r="C21" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="12" t="n">
+      <c r="D21" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G21" s="14" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>1.6</v>
+      <c r="H21" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="14" t="n">
+        <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>11.9</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>10.5</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" s="14" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2265,28 +2199,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1.6</v>
+        <v>17.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V21" s="14" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2302,75 +2236,75 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>1536.3</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="14" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>13.3</v>
+      <c r="H22" s="14" t="n">
+        <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M22" s="14" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>21.1</v>
+        <v>51</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="V22" s="14" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>216.3</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>126.2</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2384,79 +2318,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>17.1</v>
+      <c r="C23" s="3" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44255
-82947
-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.2</v>
+        <v>719.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.1</v>
+        <v>20.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>23</v>
+        <v>1212</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.4</v>
+        <v>141.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.4</v>
+        <v>154.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>4.9</v>
+        <v>182.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>292</v>
+        <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>30.5</v>
+        <v>1302.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>68.8</v>
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>17.3</v>
+        <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>192.1</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2472,76 +2404,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5026.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="D24" s="18" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>14.1</v>
+      <c r="E24" s="18" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>23.4</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>78.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>54.6</v>
+        <v>4.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="14" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U24" s="13" t="n">
-        <v>87.2</v>
+        <v>116.6</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>37.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2557,79 +2485,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>12.2</v>
+        <v>425.5</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L25" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>11.8</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>14</v>
+        <v>140</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>114</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-2
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-171111
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
+        <v>911.1</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V25" s="14" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>1457.5</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1112.1</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2646,73 +2568,71 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="D26" s="13" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G26" s="13" t="n">
         <v>15.5</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>15</v>
+      <c r="H26" s="14" t="n">
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L26" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="14" t="n">
         <v>15.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V26" s="13" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="W26" s="13" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>33.4</v>
+      </c>
+      <c r="V26" s="14" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>227</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2727,80 +2647,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>6.6</v>
+        <v>550.1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L27" s="14" t="n">
         <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>98.5</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>528</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>29.3</v>
+        <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>7.1</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>3.4</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="14" t="n">
+        <v>37.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>1026.6</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2816,80 +2724,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>621</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>1621</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G28" s="13" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>28.1</v>
+        <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>1.8</v>
+      <c r="M28" s="14" t="n">
+        <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.8</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>1428</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>120.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>30.8</v>
+        <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>166</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="V28" s="14" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W28" s="14" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.9</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
+        <v>18.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,75 +2809,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G29" s="3" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G29" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20.4</v>
+        <v>17.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.3</v>
+        <v>141.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q29" s="14" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4.6</v>
+        <v>45.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="14" t="n">
         <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n">
+        <v>3068.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2988,75 +2892,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>8.1</v>
+        <v>2781.9</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>18.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.5</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>55.8</v>
+        <v>155.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>110.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.3</v>
+        <v>130.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.3</v>
+        <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>33.5</v>
+        <v>153.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>8194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>6.8</v>
+        <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3071,71 +2971,65 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>556.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>0.4</v>
+      <c r="E31" s="13" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>11.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J31" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J31" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="13" t="n">
-        <v>92.90000000000001</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>43.1</v>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="R31" s="13" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="n">
+        <v>114.5</v>
+      </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W31" s="3" t="n">
+      <c r="V31" s="14" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="W31" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.5</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3153,70 +3047,68 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>424.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="14" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W32" s="14" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>17.1</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="n">
+        <v>31.9</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3230,74 +3122,72 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="11" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="C33" s="3" t="n">
+        <v>448.7</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G33" s="14" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>35.8</v>
+        <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" s="14" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>5.7</v>
+      <c r="M33" s="14" t="n">
+        <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="R33" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="P33" s="14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="13" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="14" t="n">
+        <v>218</v>
+      </c>
+      <c r="W33" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3314,78 +3204,70 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="D34" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>6</v>
+        <v>14.2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0.8</v>
+      <c r="M34" s="14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>116</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>12952.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R34" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>30.3</v>
+        <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V34" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="14" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+      <c r="X34" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-178
-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3403,62 +3285,60 @@
       <c r="C35" s="3" t="n">
         <v>433.9</v>
       </c>
-      <c r="D35" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>12.4</v>
+      <c r="D35" s="13" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>14.2</v>
+        <v>5.3</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>28.5</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>2.1</v>
+        <v>124</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="14" t="n">
+        <v>15.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>55</v>
+        <v>222.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
+      </c>
+      <c r="V35" s="14" t="n">
+        <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
@@ -3467,9 +3347,11 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>1839.8</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>422.1</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3484,73 +3366,73 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>13.3</v>
+        <v>341.3</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="n">
-        <v>9.1</v>
+        <v>21.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" s="14" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="M36" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R36" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>22.8</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>21.6</v>
+        <v>0.1</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W36" s="14" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="14" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>218.8</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>116.8</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3564,71 +3446,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>18.5</v>
+      <c r="C37" s="3" t="n">
+        <v>966.1</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>110.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.2</v>
+        <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>42.4</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>101</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>36.4</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>821.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>123.2</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>20.2</v>
+        <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.8</v>
+        <v>594.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>24.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.2</v>
+        <v>1782.6</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>4.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>34.1</v>
+        <v>1141</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.4</v>
+        <v>1134.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>79</v>
+        <v>0.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>49.2</v>
+        <v>949.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>183.1</v>
+        <v>181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>96.2</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3644,73 +3532,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>16.3</v>
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>22</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>111.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>36.1</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>47.8</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>1418</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="Q38" s="13" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="R38" s="13" t="n">
-        <v>48.5</v>
+        <v>16.9</v>
+      </c>
+      <c r="Q38" s="14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="R38" s="14" t="n">
+        <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>9.5</v>
+        <v>940.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>28.9</v>
+        <v>30.8</v>
+      </c>
+      <c r="U38" s="14" t="n">
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>37.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3729,47 +3613,45 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.4</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>6.5</v>
+        <v>314.6</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>80</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>15.5</v>
@@ -3778,25 +3660,23 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="U39" s="14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" s="14" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.4</v>
+        <v>396.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>22.2</v>
+        <v>226.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,74 +3692,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>51.2</v>
+        <v>617.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.2</v>
+        <v>18.3</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>16.2</v>
+      </c>
       <c r="M40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>94.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>15.5</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>1.1</v>
+        <v>19</v>
+      </c>
+      <c r="U40" s="14" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="14" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="X40" s="14" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>21</v>
+        <v>8120.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.6</v>
+        <v>1221.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3895,76 +3775,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>16.8</v>
+        <v>587.5</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5.6</v>
+        <v>16.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>18.8</v>
+        <v>49</v>
+      </c>
+      <c r="P41" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>15</v>
+        <v>29.8</v>
+      </c>
+      <c r="R41" s="14" t="n">
+        <v>15.3</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>26</v>
+        <v>122.2</v>
+      </c>
+      <c r="U41" s="14" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="V41" s="14" t="n">
+        <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>28.9</v>
+        <v>128.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3979,81 +3857,75 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-4811
-</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E42" s="12" t="n">
+      <c r="C42" s="3" t="n">
+        <v>481.1</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="n">
+        <v>920.9</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="R42" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>2.6</v>
+        <v>28.1</v>
+      </c>
+      <c r="U42" s="14" t="n">
+        <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>5.8</v>
+        <v>192.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4069,74 +3941,72 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E43" s="12" t="n">
+        <v>354</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E43" s="13" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>14.2</v>
+      <c r="F43" s="13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>98.5</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="R43" s="14" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>9.9</v>
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>28.7</v>
+        <v>201.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>24.6</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X43" s="13" t="n">
-        <v>41.8</v>
+        <v>13.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>285.3</v>
+        <v>1925.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>16.5</v>
+        <v>246.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4152,76 +4022,72 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>17.7</v>
+        <v>238</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="14" t="n">
+        <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>16.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>581.5</v>
+        <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S44" s="13" t="n">
-        <v>89.8</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q44" s="14" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R44" s="14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>21.8</v>
+        <v>109.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>1.4</v>
+        <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>8.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W44" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X44" s="14" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.6</v>
+        <v>182.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4237,78 +4103,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>15.7</v>
+        <v>33102.9</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>11871.5</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>119.1</v>
+        <v>11.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>6.1</v>
+        <v>82224.60000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>90.8</v>
+        <v>1512.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>3.5</v>
+        <v>1822.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.6</v>
+        <v>111011.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
+        <v>1815.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>0.4</v>
+        <v>11226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>22.2</v>
+        <v>133.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S45" s="3" t="n"/>
+        <v>1021.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>183.8</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>2.2</v>
+        <v>1836.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>52.8</v>
+        <v>8888.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.2</v>
+        <v>21462.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>14.7</v>
+        <v>106.1</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>1098.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-11
-</t>
-        </is>
+        <v>1222.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1117.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,68 +4186,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>232.2</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="I46" s="3" t="n">
-        <v>35</v>
+        <v>6.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>524.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>8.6</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="n">
-        <v>26.5</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="R46" s="13" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="Q46" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>751.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U46" s="14" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>64.8</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,26 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,34 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -796,49 +775,55 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1569.8</v>
-      </c>
-      <c r="D4" s="13" t="n">
+        <v>562.8</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="14" t="n">
-        <v>72.8</v>
+      <c r="H4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="14" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="R4" s="14" t="n">
+      <c r="Q4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -863,74 +848,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E5" s="13" t="n">
+        <v>15127.1</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>21.8</v>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>44.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M5" s="14" t="n">
-        <v>65.5</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="14" t="n">
-        <v>14</v>
+      <c r="R5" s="8" t="n">
+        <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="14" t="n">
+      <c r="T5" s="3" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="V5" s="14" t="n">
+      <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="14" t="n">
-        <v>10.3</v>
+      <c r="W5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>32.2</v>
+        <v>38.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -946,19 +933,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1504.8</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>2062.3</v>
+        <v>2304.8</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -970,25 +957,27 @@
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="14" t="n">
-        <v>89.8</v>
+        <v>6</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1140</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="14" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="14" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -998,22 +987,22 @@
         <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>14.2</v>
+      <c r="W6" s="8" t="n">
+        <v>64.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>201.2</v>
+        <v>20.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1031,72 +1020,74 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>8</v>
+        <v>16.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>22.1</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="R7" s="14" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>8.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U7" s="14" t="n">
-        <v>42.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W7" s="14" t="n">
-        <v>13.5</v>
+        <v>29.1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.4</v>
+        <v>23.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,37 +1103,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>485.1</v>
+        <v>11285.1</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>11.3</v>
+        <v>24.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+        <v>32.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>91</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2</v>
+        <v>81.2</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>110.8</v>
+        <v>19.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>236.5</v>
+        <v>36</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1150,33 +1145,31 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="14" t="n">
-        <v>71</v>
+      <c r="S8" s="3" t="n">
+        <v>87</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U8" s="14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="W8" s="14" t="n">
+      <c r="V8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W8" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="X8" s="14" t="n">
-        <v>11.7</v>
+      <c r="X8" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>11098.2</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1191,53 +1184,55 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>111.5</v>
-      </c>
-      <c r="G9" s="17" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1413.4</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>39.1</v>
+        <v>329.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1644.2</v>
+        <v>614.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
+        <v>32.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>258.7</v>
+        <v>121.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>949.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1169</v>
+        <v>169</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
@@ -1246,7 +1241,7 @@
         <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1139.7</v>
+        <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>169.6</v>
@@ -1258,7 +1253,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1120.2</v>
+        <v>1158.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,72 +1271,70 @@
       <c r="C10" s="3" t="n">
         <v>231.2</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>33.9</v>
+      <c r="D10" s="10" t="n">
+        <v>22.9</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>10.7</v>
+        <v>37.2</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
+        <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>99.8</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V10" s="14" t="n">
+      <c r="U10" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="14" t="n">
+      <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>17.8</v>
+      <c r="X10" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>99.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1357,33 +1350,37 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1427.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
-        <v>23.9</v>
+        <v>427.9</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>33.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.6</v>
+        <v>13.9</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>11.7</v>
+      </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16.4</v>
+        <v>61.4</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
@@ -1392,24 +1389,22 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="14" t="n">
-        <v>148.9</v>
+      <c r="R11" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="U11" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="V11" s="14" t="n">
-        <v>21.7</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1428,29 +1423,31 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G12" s="14" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n">
+        <v>6.1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1459,22 +1456,22 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q12" s="14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16.2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
@@ -1483,19 +1480,19 @@
         <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="14" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="14" t="n">
-        <v>2.3</v>
+      <c r="X12" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>47</v>
+        <v>1217</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>4.8</v>
+        <v>1835.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1511,31 +1508,31 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1601.3</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>34.4</v>
+        <v>601.3</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>34.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>15.5</v>
+        <v>59.4</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H13" s="14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
@@ -1545,40 +1542,40 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>1249</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q13" s="14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>13.8</v>
+      <c r="R13" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U13" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="14" t="n">
-        <v>10.2</v>
+      <c r="X13" s="8" t="n">
+        <v>2.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1265.4</v>
+        <v>86.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1594,21 +1591,21 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1488</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E14" s="13" t="n">
+        <v>489</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H14" s="14" t="n">
+      <c r="F14" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1623,39 +1620,47 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="P14" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>7.3</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>161.1</v>
-      </c>
-      <c r="U14" s="14" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="V14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>431.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1671,69 +1676,73 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1832.9</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>16.3</v>
+        <v>252.1</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T15" s="3" t="n">
         <v>115.4</v>
       </c>
-      <c r="U15" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="n">
+      <c r="U15" s="8" t="n">
+        <v>820.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
-        <v>123.4</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1748,22 +1757,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>2726.8</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>18.3</v>
+        <v>237.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>182391.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>97.3</v>
@@ -1772,15 +1781,17 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>10.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>189.9</v>
+        <v>189.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2952.9</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>202.8</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="O16" s="3" t="n">
         <v>2212</v>
       </c>
@@ -1788,10 +1799,10 @@
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1154.7</v>
+        <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1083.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
@@ -1800,22 +1811,22 @@
         <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1188.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1131</v>
+        <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>172.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>148.3</v>
+        <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>11245.8</v>
+        <v>1143.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1124.4</v>
+        <v>1024.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1833,19 +1844,19 @@
       <c r="C17" s="3" t="n">
         <v>315.4</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>23.6</v>
+      <c r="D17" s="13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>231.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
@@ -1855,15 +1866,17 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>942.5</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1872,19 +1885,19 @@
         <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="S17" s="14" t="n">
-        <v>87.3</v>
+        <v>14.7</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>37.6</v>
+        <v>116.4</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>81.59999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>26.3</v>
+        <v>946.5</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>14.5</v>
@@ -1893,9 +1906,11 @@
         <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>229.2</v>
-      </c>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1910,72 +1925,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>532.1</v>
+        <v>1032.1</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>12.4</v>
+        <v>22.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G18" s="13" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q18" s="14" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R18" s="14" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="U18" s="14" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="14" t="n">
-        <v>184.4</v>
+      <c r="V18" s="8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1991,18 +2010,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>33.5</v>
+        <v>596.5</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>35.4</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F19" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2011,50 +2030,56 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="14" t="n">
-        <v>92.59999999999999</v>
+      <c r="J19" s="8" t="n">
+        <v>120.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="U19" s="14" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2070,49 +2095,51 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr"/>
-      <c r="E20" s="14" t="n">
+        <v>9390.5</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="13" t="n">
         <v>17.2</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="13" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L20" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N20" s="14" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>522</v>
+        <v>25</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="14" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2124,20 +2151,20 @@
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="14" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="14" t="n">
-        <v>182.4</v>
+      <c r="V20" s="8" t="n">
+        <v>620.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>28.7</v>
+        <v>118.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2153,43 +2180,45 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.2</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G21" s="14" t="n">
+        <v>942.2</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="14" t="n">
+      <c r="H21" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="14" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="M21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="N21" s="14" t="n">
-        <v>10.5</v>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2199,28 +2228,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="14" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W21" s="14" t="n">
-        <v>14.5</v>
+      <c r="V21" s="8" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>217.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2236,21 +2265,21 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1536.3</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E22" s="13" t="n">
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" s="14" t="n">
+      <c r="F22" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2259,16 +2288,18 @@
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="14" t="n">
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
       </c>
@@ -2276,34 +2307,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>24.3</v>
+        <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U22" s="14" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="14" t="n">
+      <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>216.3</v>
+        <v>26.3</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2319,22 +2350,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="E23" s="18" t="n">
+        <v>2517.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>72.5</v>
       </c>
-      <c r="F23" s="18" t="n">
-        <v>1117.1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>86.8</v>
+      <c r="F23" s="10" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>18.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2346,49 +2377,49 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>719.1</v>
+        <v>1.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1212</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>141.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>154.4</v>
+        <v>134.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>13.5</v>
+        <v>73.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>36.6</v>
+        <v>56.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1302.6</v>
+        <v>138.8</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>1127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2404,47 +2435,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>309.5</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F24" s="18" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="14" t="n">
+      <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>4.6</v>
+        <v>34.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="14" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2459,17 +2494,15 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="W24" s="3" t="inlineStr"/>
       <c r="X24" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2485,72 +2518,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="D25" s="13" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>31.9</v>
       </c>
-      <c r="E25" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="H25" s="14" t="n">
+      <c r="E25" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="14" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="M25" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <v>114</v>
+        <v>40</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R25" s="14" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>87.3</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>120.2</v>
+        <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="V25" s="14" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="W25" s="14" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1457.5</v>
+        <v>1411.4</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>21821828</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2566,53 +2603,55 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>530.4</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F26" s="13" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>11.6</v>
+      <c r="G26" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="14" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>182</v>
+        <v>812</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.1</v>
+        <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>18</v>
@@ -2620,18 +2659,20 @@
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="14" t="n">
+      <c r="V26" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Y26" s="3" t="n">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>125</v>
+        <v>25.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2649,35 +2690,39 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="13" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>16.6</v>
+      <c r="D27" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
-        <v>10.6</v>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <v>16.3</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>22</v>
       </c>
@@ -2688,27 +2733,29 @@
         <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="T27" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="U27" s="14" t="n">
-        <v>37.4</v>
+      <c r="U27" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>1026.6</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>1865.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2724,21 +2771,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>33.2</v>
+        <v>631</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>32.9</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H28" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2748,42 +2795,42 @@
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="M28" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1428</v>
-      </c>
-      <c r="P28" s="14" t="n">
-        <v>120.8</v>
+        <v>142</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>101</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.3</v>
+        <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V28" s="14" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="14" t="n">
+      <c r="W28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2793,7 +2840,7 @@
         <v>18.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>30.8</v>
+        <v>90.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2809,62 +2856,64 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G29" s="13" t="n">
+        <v>624.8</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E29" s="12" t="n">
         <v>22.2</v>
       </c>
+      <c r="F29" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="H29" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>0.8</v>
+        <v>49.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>141.3</v>
+        <v>4.1</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Q29" s="14" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="R29" s="14" t="n">
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.6</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="14" t="n">
-        <v>27.7</v>
+      <c r="U29" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>75.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
@@ -2873,10 +2922,10 @@
         <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>18.6</v>
+        <v>118.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>3068.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2892,40 +2941,40 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
-      </c>
-      <c r="D30" s="13" t="n">
+        <v>2181.9</v>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>161.5</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="10" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="G30" s="17" t="n">
-        <v>18.7</v>
+      <c r="G30" s="13" t="n">
+        <v>18.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>372</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>155.8</v>
+        <v>139.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>110.9</v>
+        <v>118.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>130.6</v>
+        <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>222.3</v>
@@ -2934,17 +2983,19 @@
         <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>159.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="S30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>8194.1</v>
+        <v>1194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -2953,10 +3004,14 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>1190</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>42.9</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2971,19 +3026,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="13" t="n">
+        <v>856.4</v>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="13" t="n">
-        <v>17.4</v>
+      <c r="G31" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -2991,15 +3046,21 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="14" t="n">
+      <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
@@ -3009,27 +3070,29 @@
       <c r="Q31" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="14" t="n">
+      <c r="R31" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="S31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T31" s="3" t="n">
-        <v>114.5</v>
+        <v>14.5</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="14" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W31" s="14" t="n">
+      <c r="V31" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3048,66 +3111,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D32" s="13" t="n">
+        <v>6144.4</v>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="12" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="17" t="n">
-        <v>123.2</v>
+      <c r="G32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.6</v>
+        <v>62.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>94.2</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>126</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="T32" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="14" t="n">
+      <c r="U32" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W32" s="14" t="n">
+      <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3123,18 +3196,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>448.7</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G33" s="14" t="n">
+        <v>613.7</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3147,46 +3220,50 @@
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="P33" s="14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="14" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="T33" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="U33" s="3" t="inlineStr"/>
-      <c r="V33" s="14" t="n">
-        <v>218</v>
-      </c>
-      <c r="W33" s="14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X33" s="14" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>10.2</v>
+        <v>1455.4</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>1.3</v>
+        <v>103.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3202,21 +3279,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>386.6</v>
-      </c>
-      <c r="D34" s="13" t="n">
+        <v>3846.3</v>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3224,50 +3305,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="N34" s="14" t="n">
-        <v>116</v>
+      <c r="N34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>12952.2</v>
+        <v>42.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="14" t="n">
-        <v>13.4</v>
+      <c r="R34" s="8" t="n">
+        <v>32.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V34" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="W34" s="14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="14" t="n">
+      <c r="X34" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>11.6</v>
+        <v>1860.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3283,31 +3364,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>433.9</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="13" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="F35" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K35" s="14" t="n">
-        <v>28.5</v>
+        <v>5.5</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3315,42 +3396,44 @@
       <c r="M35" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>19.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R35" s="14" t="n">
-        <v>15.8</v>
+      <c r="R35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>222.8</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V35" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1839.8</v>
+        <v>23</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>422.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3368,70 +3451,74 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="13" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>14.3</v>
+      <c r="D36" s="12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J36" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L36" s="14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="14" t="n">
+      <c r="M36" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="14" t="n">
+      <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W36" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>822.1</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="14" t="n">
+      <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>218.8</v>
+        <v>1498.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3447,76 +3534,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>966.1</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>151.2</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>110.2</v>
+        <v>2216.6</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>152</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>110.7</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>15.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>101</v>
+        <v>1018</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>36.4</v>
+        <v>8.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>123.2</v>
+        <v>23.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>594.1</v>
+        <v>593.5</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.5</v>
+        <v>133.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1782.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1141</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1134.2</v>
+        <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>114.1</v>
+        <v>111.3</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0.6</v>
+        <v>87</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>949.8</v>
+        <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
+        <v>1315</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3532,57 +3619,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>443.3</v>
-      </c>
-      <c r="D38" s="13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>111.2</v>
+        <v>473.3</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>1418</v>
+        <v>18</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="14" t="n">
+      <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>940.1</v>
+        <v>12.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="U38" s="14" t="n">
-        <v>26.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3613,48 +3704,52 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>314.6</v>
+        <v>914.6</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>29.2</v>
+        <v>19.21</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>14.2</v>
+        <v>14.126</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>51.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="14" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>510.1</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>15.5</v>
+        <v>211</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>59.3</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
@@ -3662,21 +3757,23 @@
       <c r="T39" s="3" t="n">
         <v>122.4</v>
       </c>
-      <c r="U39" s="14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="14" t="n">
+      <c r="U39" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>226.6</v>
+        <v>28.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3692,40 +3789,40 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G40" s="14" t="n">
+        <v>6471.6</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I40" s="14" t="n">
-        <v>8.6</v>
+      <c r="I40" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3736,30 +3833,32 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="14" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U40" s="14" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="U40" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="V40" s="3" t="inlineStr"/>
-      <c r="W40" s="14" t="n">
+      <c r="V40" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="W40" s="8" t="n">
         <v>84.7</v>
       </c>
-      <c r="X40" s="14" t="n">
-        <v>10.1</v>
+      <c r="X40" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>8120.6</v>
+        <v>38</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1221.6</v>
+        <v>2216.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3777,17 +3876,17 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="13" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E41" s="13" t="n">
+      <c r="D41" s="12" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E41" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>15.2</v>
+        <v>166.2</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
@@ -3799,51 +3898,51 @@
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>10.1</v>
+      </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="14" t="n">
-        <v>10.8</v>
+      <c r="P41" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="14" t="n">
-        <v>15.3</v>
+      <c r="R41" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="14" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="V41" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>10.1</v>
+      <c r="X41" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1828.4</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3861,72 +3960,72 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>31.2</v>
+        <v>12.1</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>15.3</v>
+        <v>1.6</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>920.9</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="R42" s="14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="U42" s="14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3941,72 +4040,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>354</v>
+        <v>254</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E43" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G43" s="14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G43" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="M43" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="14" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="14" t="n">
+      <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>201.3</v>
+        <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22.7</v>
+        <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1925.3</v>
+        <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>246.1</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4022,33 +4125,37 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F44" s="13" t="n">
+        <v>228</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="12" t="n">
         <v>15.7</v>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="14" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="14" t="n">
+      <c r="H44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>2.8</v>
+        <v>19.8</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>8.800000000000001</v>
@@ -4057,37 +4164,37 @@
         <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q44" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="14" t="n">
+      <c r="R44" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>109.3</v>
+        <v>119.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>12.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="14" t="n">
+      <c r="W44" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="14" t="n">
-        <v>12.2</v>
+      <c r="X44" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>182.4</v>
+        <v>1122.1</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4102,76 +4209,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>33102.9</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>11871.5</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>191.9</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>132.5</v>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="10" t="n">
+        <v>1555.1</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>1102.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>21</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.2</v>
+        <v>29.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82224.60000000001</v>
+        <v>345</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1512.3</v>
+        <v>226.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1822.2</v>
+        <v>14.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111011.1</v>
+        <v>1291.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1815.9</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>11226.5</v>
+        <v>102261.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
+        <v>920.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>133.4</v>
+        <v>128.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1021.8</v>
+        <v>11.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>183.8</v>
+        <v>182</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1836.9</v>
+        <v>126.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>8888.6</v>
+        <v>102.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21462.1</v>
+        <v>141.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>106.1</v>
+        <v>101</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1098.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.8</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>1117.2</v>
-      </c>
+        <v>1222.4</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4188,63 +4293,69 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="18" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E46" s="18" t="n">
+      <c r="D46" s="10" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E46" s="13" t="n">
         <v>18.3</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>22.1</v>
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="14" t="n">
+      <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>119.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="14" t="n">
+      <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="U46" s="14" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>119.6</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,19 +152,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -775,22 +796,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>562.8</v>
-      </c>
-      <c r="D4" s="12" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -805,10 +826,10 @@
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>34.5</v>
@@ -817,9 +838,9 @@
         <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R4" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -848,40 +869,40 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15127.1</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E5" s="12" t="n">
+        <v>648.3</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E5" s="13" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>28.8</v>
+      <c r="F5" s="13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22.2</v>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -892,17 +913,17 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="14" t="n">
         <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>444.9</v>
+        <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
@@ -914,10 +935,10 @@
         <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -933,43 +954,43 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2304.8</v>
-      </c>
-      <c r="D6" s="12" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="D6" s="13" t="n">
         <v>33.8</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>10.7</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>22.4</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="13" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="14" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.8</v>
+        <v>2.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>2109.8</v>
+        <v>100.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>8.5</v>
@@ -981,28 +1002,28 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>41.8</v>
+      <c r="U6" s="14" t="n">
+        <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="8" t="n">
-        <v>64.2</v>
+      <c r="W6" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>20.2</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1020,38 +1041,38 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1060,34 +1081,34 @@
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>1.7</v>
+        <v>21.7</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.5</v>
+        <v>86.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>23.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1103,16 +1124,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>11285.1</v>
+        <v>285.1</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>11</v>
+        <v>34.4</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>21</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>32.8</v>
+        <v>27.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>23.4</v>
@@ -1121,23 +1142,23 @@
         <v>11.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="J8" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>16.1</v>
+      <c r="K8" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M8" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36</v>
+        <v>3262</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1145,11 +1166,11 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="14" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1157,17 +1178,17 @@
       <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W8" s="8" t="n">
+      <c r="V8" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>11098.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1184,37 +1205,37 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2666</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>169.7</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1413.4</v>
-      </c>
-      <c r="G9" s="13" t="n">
+        <v>19656.5</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>329.1</v>
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>614.2</v>
+        <v>14.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>121.7</v>
@@ -1223,7 +1244,7 @@
         <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>169</v>
@@ -1253,7 +1274,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1158.4</v>
+        <v>120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1269,22 +1290,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>22.9</v>
+        <v>531.2</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>34</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>37.2</v>
+        <v>12.6</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1304,7 +1325,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
@@ -1313,13 +1334,13 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="8" t="n">
-        <v>94.8</v>
+      <c r="U10" s="3" t="n">
+        <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.9</v>
@@ -1327,11 +1348,11 @@
       <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>99.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8</v>
@@ -1353,36 +1374,38 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E11" s="13" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H11" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>113</v>
       </c>
@@ -1392,17 +1415,17 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>14.9</v>
+      <c r="R11" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>822</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
@@ -1425,16 +1448,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="D12" s="15" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1461,38 +1482,38 @@
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="P12" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R12" s="8" t="n">
+      <c r="Q12" s="14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>12.9</v>
+      <c r="X12" s="14" t="n">
+        <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1217</v>
+        <v>1417</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>1835.8</v>
+        <v>18.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1510,23 +1531,21 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="13" t="n">
         <v>34.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>59.4</v>
+        <v>15.5</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="G13" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
@@ -1542,7 +1561,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>849</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
@@ -1550,8 +1569,8 @@
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15</v>
+      <c r="R13" s="14" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1565,17 +1584,17 @@
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="8" t="n">
-        <v>2.1</v>
+      <c r="X13" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>86.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1593,17 +1612,17 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="D14" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>24.4</v>
+      <c r="F14" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13.6</v>
@@ -1615,16 +1634,16 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>49</v>
@@ -1636,10 +1655,10 @@
         <v>30.3</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>73.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
@@ -1653,14 +1672,14 @@
       <c r="W14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="X14" s="8" t="n">
-        <v>81.2</v>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>80.8</v>
+        <v>1020.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.2</v>
+        <v>231.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1676,19 +1695,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>16.8</v>
+        <v>2652.1</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
@@ -1705,41 +1724,39 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4.8</v>
+        <v>148.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="14" t="n">
+        <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>820.8</v>
+        <v>15.4</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>14</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="W15" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" s="3" t="inlineStr"/>
       <c r="Z15" s="3" t="inlineStr"/>
@@ -1757,16 +1774,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>182391.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>118.2</v>
+        <v>257.2</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>8291.6</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1781,25 +1798,23 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>189.8</v>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="n">
-        <v>202.8</v>
+        <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212</v>
+        <v>2212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>184.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1808,22 +1823,22 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>188.2</v>
+        <v>128.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>172.8</v>
+        <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1143.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1024.4</v>
@@ -1842,19 +1857,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="13" t="n">
+        <v>2313.4</v>
+      </c>
+      <c r="D17" s="18" t="n">
         <v>31.9</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>231.6</v>
+      <c r="E17" s="15" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1865,18 +1880,20 @@
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="14" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1888,13 +1905,13 @@
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
-      <c r="U17" s="8" t="n">
-        <v>81.59999999999999</v>
+      <c r="U17" s="14" t="n">
+        <v>27.4</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>946.5</v>
@@ -1909,7 +1926,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>24.9</v>
+        <v>29.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,28 +1942,26 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1032.1</v>
-      </c>
-      <c r="D18" s="13" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="D18" s="15" t="n">
         <v>22.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F18" s="13" t="n">
+      <c r="E18" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>32.7</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1958,7 +1973,7 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
@@ -1966,35 +1981,35 @@
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>80.40000000000001</v>
+      <c r="Q18" s="14" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.5</v>
+        <v>118.3</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W18" s="8" t="n">
+      <c r="V18" s="14" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W18" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2010,40 +2025,38 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.5</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>35.4</v>
+        <v>596.1</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>33.5</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F19" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="13" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>120.6</v>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.5</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>17.1</v>
+        <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>60.5</v>
@@ -2054,20 +2067,20 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>61.4</v>
+      <c r="U19" s="3" t="n">
+        <v>41.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
@@ -2076,10 +2089,10 @@
         <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2095,43 +2108,43 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9390.5</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F20" s="13" t="n">
+        <v>322.8</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F20" s="15" t="n">
         <v>12.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="14" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>11.1</v>
+      <c r="N20" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2146,22 +2159,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.5</v>
+        <v>44.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="8" t="n">
-        <v>620.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2180,25 +2193,25 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>942.2</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="12" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>10.6</v>
@@ -2206,10 +2219,10 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="14" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M21" s="14" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2236,20 +2249,20 @@
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="14" t="n">
         <v>86.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>217.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2265,18 +2278,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
-      </c>
-      <c r="D22" s="12" t="n">
+        <v>936.3</v>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="13" t="n">
         <v>23.5</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="13" t="n">
         <v>16.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2298,7 +2311,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
@@ -2316,19 +2329,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>14.6</v>
+      <c r="W22" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2352,20 +2365,20 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>13.1</v>
+      <c r="D23" s="18" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>116.9</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>18.7</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2377,28 +2390,28 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>4.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>1272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>134.4</v>
+        <v>254.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.5</v>
+        <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>56.6</v>
+        <v>368.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2407,10 +2420,10 @@
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.8</v>
+        <v>138.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>42.8</v>
@@ -2419,7 +2432,7 @@
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1127.4</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2435,49 +2448,47 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>543.5</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>503.5</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="18" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>12.2</v>
+      <c r="H24" s="14" t="n">
+        <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J24" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>10.1</v>
+        <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.6</v>
+        <v>24.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.9</v>
+        <v>20.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>14.7</v>
@@ -2486,7 +2497,7 @@
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>37.4</v>
@@ -2494,15 +2505,17 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2520,16 +2533,16 @@
       <c r="C25" s="3" t="n">
         <v>455.5</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>31.9</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="13" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2541,53 +2554,53 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="14" t="n">
         <v>10.9</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <v>21.8</v>
+      <c r="M25" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>87.3</v>
+        <v>29.4</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="14" t="n">
+        <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42.8</v>
+        <v>12.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1411.4</v>
+        <v>41.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>21821828</v>
+        <v>1112.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2603,21 +2616,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>230.4</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>530.4</v>
+      </c>
+      <c r="D26" s="13" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <v>22.6</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H26" s="8" t="n">
+      <c r="G26" s="3" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H26" s="14" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2629,40 +2642,40 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="14" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>812</v>
+        <v>82</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W26" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2672,7 +2685,7 @@
         <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>25.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2688,19 +2701,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>26.1</v>
+        <v>50.1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
@@ -2708,26 +2721,26 @@
       <c r="I27" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>1.4</v>
+      <c r="J27" s="14" t="n">
+        <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>67.90000000000001</v>
+      <c r="L27" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
@@ -2739,23 +2752,25 @@
         <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>31.4</v>
+        <v>16</v>
+      </c>
+      <c r="U27" s="14" t="n">
+        <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>28.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="X27" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1865.9</v>
+        <v>196.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2771,22 +2786,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>631</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>32.9</v>
+        <v>1621</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>33.2</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>0.4</v>
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2807,30 +2822,30 @@
         <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>101</v>
+        <v>48</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>32.1</v>
+        <v>803.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="V28" s="14" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2839,9 +2854,7 @@
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>90.8</v>
-      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2858,29 +2871,29 @@
       <c r="C29" s="3" t="n">
         <v>624.8</v>
       </c>
-      <c r="D29" s="12" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="D29" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G29" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>10</v>
+        <v>49.3</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2892,15 +2905,15 @@
         <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.1</v>
+        <v>41.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2910,22 +2923,22 @@
         <v>19</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>75.7</v>
+        <v>47.1</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>10.8</v>
+        <v>23009</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2941,28 +2954,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2181.9</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
+        <v>2281.9</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="E30" s="13" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>18.1</v>
+      <c r="F30" s="13" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>139.8</v>
+        <v>23.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>118.9</v>
@@ -2980,22 +2993,22 @@
         <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>159.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>12.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -3004,13 +3017,13 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1190</v>
+        <v>110</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>13.6</v>
+        <v>106.9</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>42.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,19 +3039,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>856.4</v>
-      </c>
-      <c r="D31" s="12" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="13" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="13" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>4.8</v>
+      <c r="G31" s="13" t="n">
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -3046,11 +3059,11 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3074,7 +3087,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3111,37 +3124,37 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6144.4</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D32" s="13" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F32" s="12" t="n">
+      <c r="E32" s="13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F32" s="13" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>28.2</v>
+      <c r="G32" s="13" t="n">
+        <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>62.1</v>
+        <v>6.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>126</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1.2</v>
@@ -3150,12 +3163,12 @@
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3167,20 +3180,20 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="14" t="n">
         <v>28.3</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3196,74 +3209,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>613.7</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E33" s="12" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E33" s="13" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G33" s="12" t="n">
+      <c r="F33" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G33" s="13" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="14" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="X33" s="8" t="n">
+      <c r="W33" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="14" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1455.4</v>
+        <v>149.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>103.9</v>
+        <v>43.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3279,22 +3294,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3846.3</v>
-      </c>
-      <c r="D34" s="12" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="D34" s="13" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="13" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>1.8</v>
+      <c r="G34" s="13" t="n">
+        <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3305,17 +3320,17 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.4</v>
+      <c r="M34" s="14" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>42.2</v>
+        <v>22.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3323,11 +3338,11 @@
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>32.4</v>
+      <c r="R34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
@@ -3335,20 +3350,20 @@
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>89</v>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1860.6</v>
+        <v>1801.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3366,28 +3381,28 @@
       <c r="C35" s="3" t="n">
         <v>439.9</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="13" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="13" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="13" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
@@ -3397,18 +3412,16 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="R35" s="8" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3417,8 +3430,8 @@
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U35" s="8" t="n">
-        <v>11.1</v>
+      <c r="U35" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3430,11 +3443,9 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>19.2</v>
-      </c>
+        <v>2121.5</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3451,30 +3462,26 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="12" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E36" s="12" t="n">
+      <c r="D36" s="13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E36" s="13" t="n">
         <v>11.9</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="13" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H36" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H36" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3482,10 +3489,10 @@
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3500,25 +3507,25 @@
         <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.4</v>
+        <v>2.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>822.1</v>
-      </c>
-      <c r="W36" s="8" t="n">
+      <c r="V36" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="W36" s="14" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1498.8</v>
+        <v>1186</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>116.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3536,74 +3543,74 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D37" s="13" t="n">
         <v>152</v>
       </c>
-      <c r="E37" s="12" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>110.7</v>
+      <c r="E37" s="13" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>110.6</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>15.8</v>
+        <v>33.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1018</v>
+        <v>180</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>593.5</v>
+        <v>89.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>151.6</v>
+        <v>1151</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111.3</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>1315</v>
+        <v>1181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3619,22 +3626,22 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="D38" s="13" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>13.9</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>19.2</v>
+      <c r="G38" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
@@ -3648,32 +3655,32 @@
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.2</v>
+        <v>27.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="14" t="n">
         <v>26.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3706,71 +3713,71 @@
       <c r="C39" s="3" t="n">
         <v>914.6</v>
       </c>
-      <c r="D39" s="13" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>14.126</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="D39" s="15" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H39" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>510.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+      <c r="L39" s="14" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>59.3</v>
+      <c r="Q39" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U39" s="14" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="14" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>96.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>28.8</v>
@@ -3789,25 +3796,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6471.6</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>641.4</v>
+      </c>
+      <c r="D40" s="13" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="13" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
@@ -3815,14 +3822,14 @@
       <c r="K40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="14" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3833,7 +3840,7 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="14" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3842,23 +3849,23 @@
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.2</v>
+      <c r="U40" s="3" t="n">
+        <v>84.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.1</v>
+      <c r="W40" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2216.3</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3876,44 +3883,44 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="E41" s="12" t="n">
+      <c r="D41" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="13" t="n">
         <v>23.8</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>166.2</v>
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="14" t="n">
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>19.8</v>
+        <v>99</v>
+      </c>
+      <c r="P41" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
@@ -3925,24 +3932,24 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>22.2</v>
+        <v>122.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.6</v>
+        <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X41" s="14" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y41" s="3" t="n">
-        <v>1828.4</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3960,22 +3967,22 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>12.1</v>
+        <v>31.2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>1.6</v>
+        <v>15.5</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>7.3</v>
@@ -3983,32 +3990,32 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="14" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="14" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -4016,14 +4023,14 @@
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>13</v>
+      <c r="W42" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4040,22 +4047,22 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>254</v>
+        <v>534</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>16.4</v>
+        <v>30.6</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>16.8</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G43" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>13.4</v>
+      <c r="H43" s="14" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4069,14 +4076,14 @@
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>921.6</v>
+        <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
@@ -4084,7 +4091,7 @@
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4094,13 +4101,13 @@
         <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4109,7 +4116,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.6</v>
+        <v>124.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4127,16 +4134,16 @@
       <c r="C44" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F44" s="12" t="n">
+      <c r="D44" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="13" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4149,19 +4156,19 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4169,33 +4176,31 @@
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>7.8</v>
+        <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>12.8</v>
+        <v>112.3</v>
+      </c>
+      <c r="U44" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="8" t="n">
+      <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>12.8</v>
+      <c r="X44" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>1122.1</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4209,72 +4214,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
-        <v>1555.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>411.9</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>1102.1</v>
+      <c r="C45" s="3" t="n">
+        <v>1801.1</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>345</v>
+        <v>721.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>226.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>14.8</v>
+        <v>181.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1291.9</v>
+        <v>1281.8</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>102261.5</v>
+        <v>1226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>920.4</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>128.4</v>
+        <v>170</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>102.6</v>
-      </c>
+        <v>126.4</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="n">
-        <v>141.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>101</v>
+        <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.4</v>
+        <v>1222.9</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4291,41 +4296,43 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>1</v>
+        <v>561.8</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>33</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="14" t="n">
         <v>80.8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>119.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4334,7 +4341,7 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
@@ -4343,22 +4350,22 @@
         <v>22.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>14.4</v>
+        <v>24</v>
+      </c>
+      <c r="W46" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>112.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,19 +173,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -798,16 +804,16 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -822,7 +828,7 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="12" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -850,8 +856,8 @@
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="13" t="inlineStr"/>
+      <c r="W4" s="13" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -871,16 +877,16 @@
       <c r="C5" s="3" t="n">
         <v>648.3</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>32.9</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -895,7 +901,7 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -913,7 +919,7 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="14" t="n">
+      <c r="R5" s="15" t="n">
         <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -956,16 +962,16 @@
       <c r="C6" s="3" t="n">
         <v>306.8</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>10.7</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -980,7 +986,7 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -1007,13 +1013,13 @@
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="14" t="n">
+      <c r="U6" s="16" t="n">
         <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="15" t="n">
         <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1041,16 +1047,16 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1065,7 +1071,7 @@
       <c r="K7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="12" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
@@ -1083,7 +1089,7 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="15" t="n">
         <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1098,7 +1104,7 @@
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1126,13 +1132,13 @@
       <c r="C8" s="3" t="n">
         <v>285.1</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <v>27.7</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1144,16 +1150,16 @@
       <c r="I8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="16" t="n">
         <v>11</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="16" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1163,19 +1169,19 @@
       <c r="P8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="14" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S8" s="3" t="n">
+      <c r="R8" s="15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="12" t="n">
         <v>14.3</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="12" t="n">
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1207,13 +1213,13 @@
       <c r="C9" s="3" t="n">
         <v>19656.5</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>169.8</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>63.1</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="12" t="n">
         <v>116.4</v>
       </c>
       <c r="G9" s="15" t="n">
@@ -1228,13 +1234,13 @@
       <c r="J9" s="3" t="n">
         <v>168.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="L9" s="12" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M9" s="20" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1246,10 +1252,10 @@
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="20" t="n">
         <v>169</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="20" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1261,10 +1267,10 @@
       <c r="U9" s="3" t="n">
         <v>1224.1</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="20" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="20" t="n">
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1292,13 +1298,13 @@
       <c r="C10" s="3" t="n">
         <v>531.2</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="12" t="n">
         <v>23.3</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1314,10 +1320,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="20" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1327,10 +1333,10 @@
       <c r="P10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="20" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1342,10 +1348,10 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="20" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="20" t="n">
         <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1373,16 +1379,16 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1400,7 +1406,7 @@
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="12" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1427,8 +1433,8 @@
       <c r="U11" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="W11" s="13" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1451,8 +1457,8 @@
       <c r="D12" s="15" t="n">
         <v>51.3</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="14" t="n">
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="16" t="n">
         <v>21.7</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1473,7 +1479,7 @@
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1482,10 +1488,10 @@
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="16" t="n">
         <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1503,10 +1509,10 @@
       <c r="V12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W12" s="14" t="n">
+      <c r="W12" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="14" t="n">
+      <c r="X12" s="16" t="n">
         <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
@@ -1531,16 +1537,16 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -1556,7 +1562,7 @@
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1566,19 +1572,19 @@
       <c r="P13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="12" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="14" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S13" s="12" t="n">
         <v>6.9</v>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="12" t="n">
         <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
@@ -1612,13 +1618,13 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1639,7 +1645,7 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1654,7 +1660,7 @@
       <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="15" t="n">
         <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1706,7 +1712,7 @@
       <c r="F15" s="15" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="16" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1724,7 +1730,7 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1739,8 +1745,8 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="14" t="n">
+      <c r="R15" s="13" t="inlineStr"/>
+      <c r="S15" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
@@ -1749,10 +1755,10 @@
       <c r="U15" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="15" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="W15" s="14" t="n">
+      <c r="W15" s="16" t="n">
         <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1776,13 +1782,13 @@
       <c r="C16" s="3" t="n">
         <v>257.2</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="20" t="n">
         <v>8291.6</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="20" t="n">
         <v>21.8</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="20" t="n">
         <v>1118.2</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1797,12 +1803,12 @@
       <c r="J16" s="3" t="n">
         <v>56.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="20" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="n">
-        <v>22.1</v>
+      <c r="L16" s="19" t="inlineStr"/>
+      <c r="M16" s="12" t="n">
+        <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>4.2</v>
@@ -1813,10 +1819,10 @@
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="20" t="n">
         <v>184.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="20" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1828,10 +1834,10 @@
       <c r="U16" s="3" t="n">
         <v>128.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="20" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="20" t="n">
         <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1859,7 +1865,7 @@
       <c r="C17" s="3" t="n">
         <v>2313.4</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="20" t="n">
         <v>31.9</v>
       </c>
       <c r="E17" s="15" t="n">
@@ -1886,7 +1892,7 @@
       <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1898,10 +1904,10 @@
       <c r="P17" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="20" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="20" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1910,13 +1916,13 @@
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
-      <c r="U17" s="14" t="n">
+      <c r="U17" s="16" t="n">
         <v>27.4</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="20" t="n">
         <v>946.5</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="20" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1969,7 +1975,7 @@
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1981,10 +1987,10 @@
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="15" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1996,10 +2002,10 @@
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="14" t="n">
+      <c r="V18" s="16" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="14" t="n">
+      <c r="W18" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2027,16 +2033,16 @@
       <c r="C19" s="3" t="n">
         <v>596.1</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <v>12.4</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2049,10 +2055,10 @@
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="15" t="n">
         <v>63.5</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2064,22 +2070,22 @@
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S19" s="12" t="n">
         <v>6.1</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="12" t="n">
         <v>12.8</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="12" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="15" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2134,13 +2140,13 @@
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="L20" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="14" t="n">
+      <c r="N20" s="16" t="n">
         <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2152,7 +2158,7 @@
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2219,10 +2225,10 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" s="15" t="n">
         <v>75.7</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2234,34 +2240,34 @@
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="12" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" s="12" t="n">
         <v>7.6</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="12" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="14" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X21" s="3" t="n">
+      <c r="V21" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X21" s="12" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y21" s="3" t="n">
+      <c r="Y21" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="12" t="n">
         <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2280,16 +2286,16 @@
       <c r="C22" s="3" t="n">
         <v>936.3</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="12" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2307,7 +2313,7 @@
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2322,7 +2328,7 @@
       <c r="Q22" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2331,10 +2337,10 @@
       <c r="T22" s="3" t="n">
         <v>184.9</v>
       </c>
-      <c r="U22" s="14" t="n">
+      <c r="U22" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="14" t="n">
+      <c r="V22" s="16" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2365,16 +2371,16 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="20" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="20" t="n">
         <v>73.5</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="20" t="n">
         <v>116.9</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2386,13 +2392,13 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="20" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="20" t="n">
         <v>7.9</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="12" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2404,11 +2410,11 @@
       <c r="P23" s="3" t="n">
         <v>41.3</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="20" t="n">
         <v>254.4</v>
       </c>
-      <c r="R23" s="3" t="n">
-        <v>23.5</v>
+      <c r="R23" s="12" t="n">
+        <v>47.3</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>368.6</v>
@@ -2419,10 +2425,10 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="20" t="n">
         <v>138.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="20" t="n">
         <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2450,33 +2456,33 @@
       <c r="C24" s="3" t="n">
         <v>503.5</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="20" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="20" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="16" t="n">
         <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="14" t="n">
+      <c r="J24" s="16" t="n">
         <v>17.4</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="20" t="n">
         <v>15.8</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>18.1</v>
+      <c r="M24" s="12" t="n">
+        <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.9</v>
@@ -2487,10 +2493,10 @@
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="20" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="12" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2502,10 +2508,10 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="20" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="20" t="n">
         <v>1.6</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2533,16 +2539,16 @@
       <c r="C25" s="3" t="n">
         <v>455.5</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>31.9</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="12" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2554,13 +2560,13 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="16" t="n">
         <v>10.9</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="14" t="n">
+      <c r="M25" s="16" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2569,16 +2575,16 @@
       <c r="O25" s="3" t="n">
         <v>401</v>
       </c>
-      <c r="P25" s="14" t="n">
+      <c r="P25" s="16" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="12" t="n">
         <v>14.8</v>
       </c>
-      <c r="S25" s="14" t="n">
+      <c r="S25" s="16" t="n">
         <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
@@ -2587,7 +2593,7 @@
       <c r="U25" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="15" t="n">
         <v>3.7</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2618,19 +2624,19 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="12" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="12" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="12" t="n">
         <v>22.6</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>85.5</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="16" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2642,10 +2648,10 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="14" t="n">
+      <c r="L26" s="16" t="n">
         <v>13.9</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="M26" s="16" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2657,10 +2663,10 @@
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="15" t="n">
         <v>99.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2675,7 +2681,7 @@
       <c r="V26" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="W26" s="14" t="n">
+      <c r="W26" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2703,16 +2709,16 @@
       <c r="C27" s="3" t="n">
         <v>50.1</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2721,7 +2727,7 @@
       <c r="I27" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="16" t="n">
         <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
@@ -2745,7 +2751,7 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2754,13 +2760,13 @@
       <c r="T27" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U27" s="14" t="n">
+      <c r="U27" s="16" t="n">
         <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2788,19 +2794,19 @@
       <c r="C28" s="3" t="n">
         <v>1621</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="12" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="16" t="n">
         <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2824,13 +2830,13 @@
       <c r="O28" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="P28" s="14" t="n">
+      <c r="P28" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>803.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="15" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2842,7 +2848,7 @@
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="14" t="n">
+      <c r="V28" s="16" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2871,16 +2877,16 @@
       <c r="C29" s="3" t="n">
         <v>624.8</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="12" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2892,7 +2898,7 @@
       <c r="J29" s="3" t="n">
         <v>49.3</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="16" t="n">
         <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
@@ -2910,10 +2916,10 @@
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="15" t="n">
         <v>83.5</v>
       </c>
-      <c r="R29" s="14" t="n">
+      <c r="R29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2956,13 +2962,13 @@
       <c r="C30" s="3" t="n">
         <v>2281.9</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="12" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="12" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="12" t="n">
         <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2977,13 +2983,13 @@
       <c r="J30" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="20" t="n">
         <v>118.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="20" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="20" t="n">
         <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2995,11 +3001,11 @@
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="20" t="n">
         <v>155.1</v>
       </c>
-      <c r="R30" s="3" t="n">
-        <v>0.9</v>
+      <c r="R30" s="12" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.8</v>
@@ -3010,10 +3016,10 @@
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="20" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="20" t="n">
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3041,16 +3047,16 @@
       <c r="C31" s="3" t="n">
         <v>236.4</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="12" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3065,10 +3071,10 @@
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="20" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="20" t="n">
         <v>110.1</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3080,10 +3086,10 @@
       <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3095,10 +3101,10 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="20" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="20" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3126,16 +3132,16 @@
       <c r="C32" s="3" t="n">
         <v>61.1</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
         <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3150,7 +3156,7 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="15" t="n">
         <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3180,19 +3186,19 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="14" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X32" s="3" t="n">
+      <c r="V32" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W32" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X32" s="12" t="n">
         <v>7.1</v>
       </c>
-      <c r="Y32" s="3" t="n">
+      <c r="Y32" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="Z32" s="3" t="n">
+      <c r="Z32" s="12" t="n">
         <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3211,16 +3217,16 @@
       <c r="C33" s="3" t="n">
         <v>122.5</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>31.5</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="12" t="n">
         <v>22.8</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3238,7 +3244,7 @@
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3262,7 +3268,7 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="14" t="n">
+      <c r="U33" s="16" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
@@ -3271,7 +3277,7 @@
       <c r="W33" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="X33" s="14" t="n">
+      <c r="X33" s="16" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3296,16 +3302,16 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3323,7 +3329,7 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="15" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3381,16 +3387,16 @@
       <c r="C35" s="3" t="n">
         <v>439.9</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3420,7 +3426,7 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="Q35" s="13" t="inlineStr"/>
       <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
@@ -3462,26 +3468,26 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="12" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="12" t="n">
         <v>11.9</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="F36" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="H36" s="14" t="n">
+      <c r="H36" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3512,10 +3518,10 @@
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="15" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="W36" s="14" t="n">
+      <c r="W36" s="16" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3543,13 +3549,13 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="12" t="n">
         <v>79.7</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="F37" s="12" t="n">
         <v>110.6</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3564,13 +3570,13 @@
       <c r="J37" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="20" t="n">
         <v>3.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="20" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="20" t="n">
         <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3582,10 +3588,10 @@
       <c r="P37" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="20" t="n">
         <v>133.5</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="20" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3597,10 +3603,10 @@
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="20" t="n">
         <v>114.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="20" t="n">
         <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3628,13 +3634,13 @@
       <c r="C38" s="3" t="n">
         <v>442.2</v>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="12" t="n">
         <v>22.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3652,10 +3658,10 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="20" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="20" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3667,10 +3673,10 @@
       <c r="P38" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="20" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="20" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3682,10 +3688,10 @@
       <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="20" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="20" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3725,7 +3731,7 @@
       <c r="G39" s="15" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H39" s="14" t="n">
+      <c r="H39" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3737,7 +3743,7 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="14" t="n">
+      <c r="L39" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3752,10 +3758,10 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>28.7</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="12" t="n">
         <v>15.5</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3764,16 +3770,16 @@
       <c r="T39" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U39" s="14" t="n">
+      <c r="U39" s="16" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="16" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3798,19 +3804,19 @@
       <c r="C40" s="3" t="n">
         <v>641.4</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="12" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F40" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3822,7 +3828,7 @@
       <c r="K40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3837,10 +3843,10 @@
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="14" t="n">
+      <c r="R40" s="12" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3852,7 +3858,7 @@
       <c r="U40" s="3" t="n">
         <v>84.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3883,16 +3889,16 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3907,10 +3913,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="14" t="n">
+      <c r="L41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="14" t="n">
+      <c r="M41" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3919,13 +3925,13 @@
       <c r="O41" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P41" s="14" t="n">
+      <c r="P41" s="16" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="12" t="n">
         <v>15.5</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3937,13 +3943,13 @@
       <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="X41" s="14" t="n">
+      <c r="X41" s="16" t="n">
         <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="inlineStr"/>
@@ -3966,16 +3972,16 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="F42" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G42" s="14" t="n">
+      <c r="G42" s="16" t="n">
         <v>18.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3990,10 +3996,10 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="14" t="n">
+      <c r="L42" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="16" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4005,25 +4011,25 @@
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>26.4</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
+      <c r="R42" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="S42" s="12" t="n">
         <v>9.9</v>
       </c>
-      <c r="T42" s="3" t="n">
+      <c r="T42" s="12" t="n">
         <v>28.7</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="14" t="n">
+      <c r="W42" s="16" t="n">
         <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4049,19 +4055,19 @@
       <c r="C43" s="3" t="n">
         <v>534</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="G43" s="16" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="16" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4073,7 +4079,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>17.7</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4088,22 +4094,22 @@
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="12" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S43" s="3" t="n">
+      <c r="R43" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S43" s="12" t="n">
         <v>8.5</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="T43" s="12" t="n">
         <v>21.3</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="U43" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
@@ -4134,16 +4140,16 @@
       <c r="C44" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F44" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4158,10 +4164,10 @@
       <c r="K44" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="15" t="n">
         <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4173,10 +4179,10 @@
       <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4185,10 +4191,10 @@
       <c r="T44" s="3" t="n">
         <v>112.3</v>
       </c>
-      <c r="U44" s="14" t="n">
+      <c r="U44" s="16" t="n">
         <v>22.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4217,13 +4223,13 @@
       <c r="C45" s="3" t="n">
         <v>1801.1</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="20" t="n">
         <v>185.1</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="20" t="n">
         <v>91.7</v>
       </c>
-      <c r="F45" s="18" t="n">
+      <c r="F45" s="20" t="n">
         <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4238,13 +4244,13 @@
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="20" t="n">
         <v>181.2</v>
       </c>
-      <c r="L45" s="3" t="n">
-        <v>1281.8</v>
-      </c>
-      <c r="M45" s="3" t="n">
+      <c r="L45" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M45" s="20" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4256,11 +4262,11 @@
       <c r="P45" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>81.5</v>
+      <c r="Q45" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>71.8</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>180</v>
@@ -4269,10 +4275,10 @@
         <v>126.4</v>
       </c>
       <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="n">
-        <v>144.2</v>
-      </c>
-      <c r="W45" s="3" t="n">
+      <c r="V45" s="12" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="W45" s="20" t="n">
         <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4298,13 +4304,13 @@
       <c r="C46" s="3" t="n">
         <v>561.8</v>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="20" t="n">
         <v>40.6</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="20" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="20" t="n">
         <v>33</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4322,10 +4328,10 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="14" t="n">
+      <c r="M46" s="20" t="n">
         <v>80.8</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4337,10 +4343,10 @@
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="12" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="12" t="n">
         <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4352,10 +4358,10 @@
       <c r="U46" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="W46" s="14" t="n">
+      <c r="W46" s="20" t="n">
         <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,31 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,9 +168,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -804,62 +783,62 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="9" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O4" s="3" t="n">
+      <c r="M4" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>35.5</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R4" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S4" s="9" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="T4" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="U4" s="9" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V4" s="12" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr"/>
+      <c r="V4" s="10" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -877,18 +856,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -900,50 +879,52 @@
       <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="9" t="n">
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Q5" s="9" t="n">
+      <c r="M5" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="n">
         <v>34.1</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y5" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="8" t="n">
         <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -962,17 +943,17 @@
       <c r="C6" s="3" t="n">
         <v>504.8</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>33.9</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="18" t="n">
-        <v>23.9</v>
+      <c r="G6" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -983,51 +964,53 @@
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+      <c r="N6" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>34.9</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="X6" s="3" t="n">
+      <c r="W6" s="15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X6" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+      <c r="Z6" s="8" t="n">
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1045,16 +1028,16 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>35.3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1066,52 +1049,52 @@
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+      <c r="N7" s="8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>39.6</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>116.3</v>
-      </c>
-      <c r="Z7" s="3" t="n">
+      <c r="W7" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Z7" s="8" t="n">
         <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1130,16 +1113,16 @@
       <c r="C8" s="3" t="n">
         <v>485.1</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1148,44 +1131,46 @@
       <c r="I8" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Q8" s="9" t="n">
+      <c r="N8" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>34.8</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W8" s="18" t="n">
+      <c r="W8" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1211,18 +1196,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>2656</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>169.7</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>53.3</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>111.4</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="15" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1234,53 +1219,53 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="20" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="9" t="n">
+      <c r="K9" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="8" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Q9" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="V9" s="20" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="V9" s="11" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="20" t="n">
-        <v>169.6</v>
+      <c r="W9" s="11" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>120.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1298,20 +1283,20 @@
       <c r="C10" s="3" t="n">
         <v>531.2</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="D10" s="8" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="18" t="n">
-        <v>47.8</v>
+      <c r="H10" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1320,45 +1305,47 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="20" t="n">
+      <c r="M10" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="Q10" s="9" t="n">
+      <c r="N10" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="V10" s="20" t="n">
+      <c r="V10" s="11" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="20" t="n">
-        <v>19.9</v>
+      <c r="W10" s="11" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1106.2</v>
+        <v>106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>21.2</v>
@@ -1377,52 +1364,52 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E11" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="17" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="18" t="n">
-        <v>46.9</v>
+      <c r="I11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L11" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>6.4</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Q11" s="9" t="n">
+      <c r="N11" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>14.9</v>
+      <c r="R11" s="8" t="n">
+        <v>5.7</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1430,18 +1417,24 @@
       <c r="T11" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" s="18" t="n">
+      <c r="U11" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="W11" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Z11" s="8" t="n">
+        <v>9.4</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1458,14 +1451,16 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="18" t="n">
+      <c r="E12" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1477,52 +1472,52 @@
       <c r="J12" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="N12" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="P12" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+      <c r="N12" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R12" s="17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S12" s="3" t="n">
+      <c r="R12" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S12" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="18" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" s="18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y12" s="3" t="n">
+      <c r="U12" s="8" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Y12" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1541,19 +1536,19 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1562,50 +1557,52 @@
       <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q13" s="9" t="n">
+      <c r="N13" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="18" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S13" s="8" t="n">
         <v>6.9</v>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="V13" s="9" t="n">
+      <c r="U13" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>7.3</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1624,16 +1621,16 @@
       <c r="C14" s="3" t="n">
         <v>488</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G14" s="9" t="n">
+      <c r="F14" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1645,51 +1642,53 @@
       <c r="J14" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+      <c r="M14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="18" t="n">
+      <c r="R14" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U14" s="18" t="n">
-        <v>236</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>114.4</v>
+      <c r="X14" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1705,18 +1704,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.9</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E15" s="9" t="n">
+        <v>552.1</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G15" s="9" t="n">
+      <c r="F15" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1728,51 +1727,53 @@
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="n">
-        <v>418</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q15" s="9" t="n">
+      <c r="N15" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="U15" s="3" t="n">
+      <c r="R15" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U15" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="X15" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>23.4</v>
+      <c r="X15" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="8" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="Z15" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1788,40 +1789,40 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.7</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="20" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>76.8</v>
       </c>
-      <c r="F16" s="20" t="n">
-        <v>2118.2</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="8" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G16" s="8" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>397.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>136.2</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L16" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="M16" s="20" t="n">
+      <c r="M16" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>212.5</v>
@@ -1829,35 +1830,35 @@
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>154.7</v>
       </c>
-      <c r="R16" s="20" t="n">
-        <v>173.6</v>
+      <c r="R16" s="8" t="n">
+        <v>12.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>188.2</v>
       </c>
-      <c r="V16" s="20" t="n">
-        <v>131.3</v>
-      </c>
-      <c r="W16" s="20" t="n">
-        <v>12.8</v>
+      <c r="V16" s="11" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>60.3</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1145.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1224.4</v>
+        <v>124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1873,25 +1874,25 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F17" s="17" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
@@ -1899,50 +1900,50 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="20" t="n">
+      <c r="M17" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+      <c r="N17" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="20" t="n">
+      <c r="R17" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>7.3</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>37.6</v>
       </c>
-      <c r="V17" s="20" t="n">
+      <c r="V17" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="W17" s="20" t="n">
+      <c r="W17" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>24.9</v>
+      <c r="X17" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1958,18 +1959,18 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G18" s="9" t="n">
+        <v>552.1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -1979,26 +1980,26 @@
         <v>8</v>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q18" s="18" t="n">
-        <v>29.1</v>
+      <c r="L18" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -2007,25 +2008,25 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
+        <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="17" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="X18" s="3" t="n">
+      <c r="W18" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X18" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y18" s="3" t="n">
+      <c r="Y18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+      <c r="Z18" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2041,18 +2042,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2061,56 +2062,56 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="Z19" s="8" t="n">
         <v>20.6</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q19" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="R19" s="9" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S19" s="9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="T19" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="V19" s="18" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>28.7</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2128,13 +2129,13 @@
       <c r="C20" s="3" t="n">
         <v>322.5</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2149,53 +2150,53 @@
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L20" s="18" t="n">
+      <c r="K20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+      <c r="N20" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="18" t="n">
+      <c r="W20" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="X20" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+      <c r="X20" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="Y20" s="8" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Z20" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2211,22 +2212,22 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>542.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2234,53 +2235,53 @@
       <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+      <c r="N21" s="8" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q21" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" s="8" t="n">
         <v>7.6</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="U21" s="3" t="n">
+      <c r="T21" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U21" s="8" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>44.6</v>
+      <c r="X21" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2298,13 +2299,13 @@
       <c r="C22" s="3" t="n">
         <v>536.3</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2316,54 +2317,56 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="18" t="n">
+      <c r="M22" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="N22" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S22" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="18" t="n">
+      <c r="T22" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U22" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>26.2</v>
+      <c r="X22" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="Z22" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2379,51 +2382,51 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2517.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>150.6</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>112</v>
+        <v>2547.5</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>111.9</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="K23" s="20" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="20" t="n">
+      <c r="L23" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="M23" s="20" t="n">
+      <c r="M23" s="8" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Q23" s="20" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>154.4</v>
       </c>
-      <c r="R23" s="14" t="inlineStr"/>
+      <c r="R23" s="13" t="inlineStr"/>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
@@ -2433,14 +2436,14 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="20" t="n">
+      <c r="V23" s="8" t="n">
         <v>130.5</v>
       </c>
-      <c r="W23" s="20" t="n">
-        <v>168.8</v>
+      <c r="W23" s="11" t="n">
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
@@ -2464,16 +2467,16 @@
       <c r="C24" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2488,22 +2491,22 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="20" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M24" s="20" t="n">
+      <c r="L24" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>294.6</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q24" s="20" t="n">
+      <c r="N24" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q24" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2518,20 +2521,20 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="20" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="20" t="n">
+      <c r="W24" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>23.5</v>
+      <c r="X24" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2547,18 +2550,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="9" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2570,53 +2573,53 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="8" t="n">
         <v>59.9</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>11.4</v>
+      <c r="Q25" s="15" t="n">
+        <v>1.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="S25" s="18" t="n">
+      <c r="S25" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U25" s="18" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V25" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="W25" s="18" t="n">
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="18" t="n">
+      <c r="X25" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>457.3</v>
+        <v>45.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2634,20 +2637,20 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>2.8</v>
+      <c r="F26" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>7.3</v>
@@ -2655,50 +2658,50 @@
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="8" t="n">
         <v>70.3</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="8" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="U26" s="18" t="n">
+      <c r="R26" s="15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U26" s="8" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W26" s="18" t="n">
+      <c r="W26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>25</v>
@@ -2719,73 +2722,73 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="U27" s="3" t="n">
+      <c r="R27" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="U27" s="8" t="n">
         <v>37.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="Z27" s="3" t="n">
+      <c r="W27" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Z27" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -2804,44 +2807,44 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="18" t="n">
-        <v>18.1</v>
+      <c r="G28" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="P28" s="9" t="n">
-        <v>6.3</v>
+      <c r="M28" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>32.1</v>
@@ -2850,15 +2853,15 @@
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>598.4</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="V28" s="9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2889,16 +2892,16 @@
       <c r="C29" s="3" t="n">
         <v>624.9</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E29" s="9" t="n">
+      <c r="D29" s="8" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="F29" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2910,53 +2913,53 @@
       <c r="J29" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>7.3</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>65.3</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="S29" s="3" t="n">
+      <c r="R29" s="15" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="S29" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="T29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="18" t="n">
+      <c r="T29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="8" t="n">
         <v>47.1</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X29" s="3" t="n">
+      <c r="W29" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>6.9</v>
       </c>
-      <c r="Y29" s="3" t="n">
+      <c r="Y29" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z29" s="3" t="n">
-        <v>30.8</v>
+      <c r="Z29" s="8" t="n">
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2974,34 +2977,34 @@
       <c r="C30" s="3" t="n">
         <v>2781.9</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L30" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L30" s="8" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="11" t="n">
         <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3011,27 +3014,27 @@
         <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="Q30" s="20" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="R30" s="20" t="n">
-        <v>20.9</v>
+        <v>51.7</v>
+      </c>
+      <c r="Q30" s="11" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="20" t="n">
+      <c r="W30" s="11" t="n">
         <v>66.8</v>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3055,18 +3058,18 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>336.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3075,33 +3078,33 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="11" t="n">
         <v>10.1</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="8" t="n">
         <v>66.3</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" s="8" t="n">
         <v>6.3</v>
       </c>
-      <c r="Q31" s="20" t="n">
+      <c r="Q31" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="20" t="n">
+      <c r="R31" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3109,17 +3112,17 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="20" t="n">
+      <c r="W31" s="11" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>21.6</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>1.8</v>
@@ -3138,18 +3141,18 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="D32" s="9" t="n">
+        <v>611.1</v>
+      </c>
+      <c r="D32" s="8" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -3160,40 +3163,40 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>1141.1</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>484.1</v>
-      </c>
-      <c r="V32" s="17" t="n">
-        <v>90.8</v>
+      <c r="S32" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>28.5</v>
@@ -3219,25 +3222,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>443.7</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E33" s="9" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G33" s="9" t="n">
+      <c r="F33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3245,50 +3248,50 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="18" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+      <c r="N33" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q33" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="18" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
+      <c r="R33" s="8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="18" t="n">
-        <v>83.40000000000001</v>
+      <c r="U33" s="8" t="n">
+        <v>23.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X33" s="18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3306,23 +3309,23 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>39.8</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>6.6</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3330,50 +3333,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q34" s="9" t="n">
+      <c r="N34" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>9.9</v>
+      <c r="S34" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="18" t="n">
-        <v>11.8</v>
+      <c r="X34" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3391,58 +3394,58 @@
       <c r="C35" s="3" t="n">
         <v>433.9</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>47.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R35" s="17" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T35" s="3" t="n">
+      <c r="N35" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="T35" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U35" s="8" t="n">
         <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
@@ -3452,7 +3455,7 @@
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0.2</v>
@@ -3476,17 +3479,17 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G36" s="18" t="n">
-        <v>4.8</v>
+      <c r="G36" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
@@ -3497,51 +3500,51 @@
       <c r="J36" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K36" s="12" t="inlineStr"/>
-      <c r="L36" s="3" t="n">
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+      <c r="N36" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q36" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S36" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="8" t="n">
         <v>34.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="V36" s="17" t="n">
-        <v>82.09999999999999</v>
+      <c r="U36" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="18" t="n">
-        <v>80.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>146.6</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>16.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3559,16 +3562,16 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="F37" s="9" t="n">
+      <c r="D37" s="11" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>110.3</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="8" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3580,51 +3583,51 @@
       <c r="J37" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="20" t="n">
+      <c r="K37" s="11" t="n">
         <v>36.1</v>
       </c>
-      <c r="L37" s="20" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="M37" s="20" t="n">
-        <v>153.2</v>
+      <c r="L37" s="8" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>53.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>2409.2</v>
+        <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>134</v>
-      </c>
-      <c r="R37" s="20" t="n">
-        <v>82.59999999999999</v>
+        <v>59.3</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>171.6</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="20" t="n">
-        <v>1141.1</v>
-      </c>
-      <c r="W37" s="20" t="n">
-        <v>97</v>
+      <c r="V37" s="11" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>188.2</v>
+        <v>187.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3642,62 +3645,62 @@
       <c r="C38" s="3" t="n">
         <v>443.3</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F38" s="9" t="n">
+      <c r="E38" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F38" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="20" t="n">
+      <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="20" t="n">
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N38" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+      <c r="N38" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="20" t="n">
+      <c r="R38" s="11" t="n">
         <v>14.5</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U38" s="18" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="V38" s="20" t="n">
+      <c r="S38" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V38" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="20" t="n">
+      <c r="W38" s="11" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3723,63 +3726,63 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5914.6</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>514.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="18" t="n">
+      <c r="H39" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O39" s="9" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="P39" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q39" s="9" t="n">
+      <c r="O39" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q39" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S39" s="3" t="n">
+      <c r="R39" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="T39" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U39" s="18" t="n">
+      <c r="T39" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3808,21 +3811,21 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3834,22 +3837,22 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N40" s="9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="O40" s="9" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="P40" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+      <c r="L40" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3862,22 +3865,22 @@
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V40" s="17" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X40" s="18" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="X40" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="Y40" s="3" t="n">
-        <v>318</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>223.6</v>
+      <c r="Y40" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z40" s="8" t="n">
+        <v>23.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3895,20 +3898,20 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="18" t="n">
-        <v>53</v>
+      <c r="H41" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3919,47 +3922,47 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N41" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O41" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="P41" s="9" t="n">
+      <c r="L41" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>7.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="N41" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q41" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>5.9</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.9</v>
+        <v>28.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>26.4</v>
@@ -3980,16 +3983,16 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4004,50 +4007,50 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>68.2</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>6.1</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
+      <c r="R42" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="S42" s="8" t="n">
         <v>9.9</v>
       </c>
-      <c r="T42" s="3" t="n">
-        <v>128.7</v>
-      </c>
-      <c r="U42" s="3" t="n">
+      <c r="T42" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U42" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1392</v>
+        <v>52</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4063,21 +4066,21 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>554</v>
+      </c>
+      <c r="D43" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="H43" s="18" t="n">
+      <c r="H43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4087,24 +4090,24 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L43" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="8" t="n">
         <v>68.8</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="8" t="n">
         <v>6.3</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4114,24 +4117,24 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="U43" s="18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W43" s="17" t="n">
+      <c r="W43" s="15" t="n">
         <v>4.5</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y43" s="9" t="n">
+      <c r="Y43" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4150,16 +4153,16 @@
       <c r="C44" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4172,52 +4175,52 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L44" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L44" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="N44" s="9" t="n">
+      <c r="N44" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="O44" s="9" t="n">
+      <c r="O44" s="8" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="P44" s="9" t="n">
+      <c r="P44" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="18" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>87.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="U44" s="18" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X44" s="18" t="n">
-        <v>227.9</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>290.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>112.4</v>
+      <c r="W44" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Y44" s="8" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Z44" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4233,68 +4236,68 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2312.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>183.8</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>137.9</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>91.09999999999999</v>
+      <c r="G45" s="3" t="n">
+        <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>7194.9</v>
+        <v>21.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="20" t="n">
+      <c r="K45" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="L45" s="9" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>64.3</v>
+      <c r="L45" s="8" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>55.8</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>296.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2908.4</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>173</v>
       </c>
-      <c r="R45" s="14" t="inlineStr"/>
+      <c r="R45" s="13" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>182.8</v>
+        <v>23.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>136.9</v>
+        <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>182.6</v>
       </c>
-      <c r="V45" s="20" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="W45" s="20" t="n">
-        <v>286.2</v>
+      <c r="V45" s="8" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="W45" s="11" t="n">
+        <v>22.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>164.7</v>
+        <v>54.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4314,72 +4317,74 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>22.3</v>
+      <c r="F46" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" s="8" t="n">
         <v>67.7</v>
       </c>
-      <c r="P46" s="9" t="n">
+      <c r="P46" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S46" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="T46" s="3" t="n">
+      <c r="R46" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="18" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="V46" s="20" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="20" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="X46" s="18" t="n">
-        <v>16.8</v>
+      <c r="U46" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W46" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,13 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -837,8 +843,8 @@
       <c r="U4" s="8" t="n">
         <v>35.5</v>
       </c>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr"/>
+      <c r="V4" s="11" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -856,7 +862,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>12.7</v>
+        <v>512.7</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>32.6</v>
@@ -915,7 +921,7 @@
       <c r="V5" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="15" t="n">
+      <c r="W5" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="X5" s="8" t="n">
@@ -1000,7 +1006,7 @@
       <c r="V6" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="15" t="n">
+      <c r="W6" s="16" t="n">
         <v>3.9</v>
       </c>
       <c r="X6" s="8" t="n">
@@ -1085,7 +1091,7 @@
       <c r="V7" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="W7" s="15" t="n">
+      <c r="W7" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="X7" s="8" t="n">
@@ -1202,12 +1208,12 @@
         <v>169.7</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>111.4</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="16" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1252,10 +1258,10 @@
       <c r="U9" s="3" t="n">
         <v>224.1</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="14" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="14" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1335,10 +1341,10 @@
       <c r="U10" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="14" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="14" t="n">
         <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1364,18 +1370,18 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.9</v>
+        <v>427.9</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1619,7 +1625,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>31.8</v>
@@ -1731,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>10.4</v>
@@ -1740,10 +1746,10 @@
         <v>12.6</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>67.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>31</v>
@@ -1791,10 +1797,10 @@
       <c r="C16" s="3" t="n">
         <v>257.7</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="14" t="n">
         <v>159.6</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="14" t="n">
         <v>76.8</v>
       </c>
       <c r="F16" s="8" t="n">
@@ -1810,22 +1816,22 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>36.2</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>89.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>218.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
@@ -1845,8 +1851,8 @@
       <c r="U16" s="3" t="n">
         <v>188.2</v>
       </c>
-      <c r="V16" s="11" t="n">
-        <v>131.5</v>
+      <c r="V16" s="14" t="n">
+        <v>131.3</v>
       </c>
       <c r="W16" s="8" t="n">
         <v>60.3</v>
@@ -1874,7 +1880,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>15.4</v>
+        <v>515.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>31.9</v>
@@ -1885,8 +1891,8 @@
       <c r="F17" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>18.5</v>
+      <c r="G17" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1930,7 +1936,7 @@
       <c r="U17" s="8" t="n">
         <v>37.6</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="14" t="n">
         <v>26.3</v>
       </c>
       <c r="W17" s="8" t="n">
@@ -1959,16 +1965,16 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>552.1</v>
+        <v>352.1</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.9</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>20.5</v>
@@ -2001,22 +2007,22 @@
       <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="S18" s="3" t="n">
+      <c r="R18" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S18" s="8" t="n">
         <v>7.4</v>
       </c>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="U18" s="3" t="n">
-        <v>22.2</v>
+      <c r="U18" s="8" t="n">
+        <v>40.4</v>
       </c>
       <c r="V18" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="15" t="n">
+      <c r="W18" s="16" t="n">
         <v>4.5</v>
       </c>
       <c r="X18" s="8" t="n">
@@ -2045,10 +2051,10 @@
         <v>526.4</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>22.9</v>
@@ -2101,17 +2107,17 @@
       <c r="V19" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>12.9</v>
+      <c r="W19" s="16" t="n">
+        <v>1.3</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>14.9</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>41.9</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>20.6</v>
+        <v>28.7</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2130,15 +2136,15 @@
         <v>322.5</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>23.4</v>
+        <v>31.4</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G20" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G20" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2218,10 +2224,10 @@
         <v>30.9</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>14.5</v>
@@ -2385,25 +2391,25 @@
         <v>2547.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>150.5</v>
+        <v>158.4</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="G23" s="3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="G23" s="8" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>3.3</v>
@@ -2415,7 +2421,7 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>273</v>
@@ -2426,7 +2432,9 @@
       <c r="Q23" s="8" t="n">
         <v>154.4</v>
       </c>
-      <c r="R23" s="13" t="inlineStr"/>
+      <c r="R23" s="8" t="n">
+        <v>12.2</v>
+      </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
@@ -2439,7 +2447,7 @@
       <c r="V23" s="8" t="n">
         <v>130.5</v>
       </c>
-      <c r="W23" s="11" t="n">
+      <c r="W23" s="14" t="n">
         <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2509,8 +2517,8 @@
       <c r="Q24" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R24" s="3" t="n">
-        <v>14.7</v>
+      <c r="R24" s="8" t="n">
+        <v>2.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
@@ -2524,7 +2532,7 @@
       <c r="V24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="14" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2591,8 +2599,8 @@
       <c r="P25" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q25" s="15" t="n">
-        <v>1.4</v>
+      <c r="Q25" s="16" t="n">
+        <v>1.1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2644,10 +2652,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2679,7 +2687,7 @@
       <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="15" t="n">
+      <c r="R26" s="16" t="n">
         <v>2.7</v>
       </c>
       <c r="S26" s="8" t="n">
@@ -2764,7 +2772,7 @@
       <c r="Q27" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="15" t="n">
+      <c r="R27" s="16" t="n">
         <v>2.1</v>
       </c>
       <c r="S27" s="8" t="n">
@@ -2856,10 +2864,10 @@
         <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>19.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
+        <v>13.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2901,8 +2909,8 @@
       <c r="F29" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>22.2</v>
+      <c r="G29" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2934,7 +2942,7 @@
       <c r="Q29" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="15" t="n">
+      <c r="R29" s="16" t="n">
         <v>-3.9</v>
       </c>
       <c r="S29" s="8" t="n">
@@ -2949,7 +2957,7 @@
       <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="15" t="n">
+      <c r="W29" s="16" t="n">
         <v>1.7</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -2975,7 +2983,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
+        <v>271.9</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>161.6</v>
@@ -2983,7 +2991,7 @@
       <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="14" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="8" t="n">
@@ -2996,7 +3004,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>25.8</v>
+        <v>35.8</v>
       </c>
       <c r="K30" s="8" t="n">
         <v>10.9</v>
@@ -3004,7 +3012,7 @@
       <c r="L30" s="8" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" s="14" t="n">
         <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3016,14 +3024,14 @@
       <c r="P30" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" s="14" t="n">
         <v>155.1</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="14" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>72.59999999999999</v>
@@ -3034,7 +3042,7 @@
       <c r="V30" s="8" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="14" t="n">
         <v>66.8</v>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3085,7 +3093,7 @@
       <c r="L31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M31" s="14" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="8" t="n">
@@ -3097,14 +3105,14 @@
       <c r="P31" s="8" t="n">
         <v>6.3</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="14" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3115,17 +3123,17 @@
       <c r="V31" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>21.6</v>
+        <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3222,7 +3230,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>43.7</v>
+        <v>243.7</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>31.3</v>
@@ -3267,16 +3275,16 @@
         <v>26</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>7.3</v>
+        <v>14.7</v>
       </c>
       <c r="S33" s="8" t="n">
-        <v>10.2</v>
+        <v>16.7</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>30.3</v>
+        <v>49.7</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>23.4</v>
+        <v>16.9</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3325,7 +3333,7 @@
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3373,10 +3381,10 @@
         <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3480,15 +3488,15 @@
         <v>341.3</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3500,7 +3508,7 @@
       <c r="J36" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K36" s="10" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
@@ -3541,7 +3549,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>40</v>
+        <v>20.2</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3562,10 +3570,10 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="14" t="n">
         <v>151.6</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="14" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="F37" s="8" t="n">
@@ -3575,7 +3583,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.8</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3583,7 +3591,7 @@
       <c r="J37" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="14" t="n">
         <v>36.1</v>
       </c>
       <c r="L37" s="8" t="n">
@@ -3599,12 +3607,12 @@
         <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.3</v>
+        <v>39.3</v>
       </c>
       <c r="Q37" s="8" t="n">
         <v>133.5</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="14" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3616,11 +3624,11 @@
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="14" t="n">
         <v>114.1</v>
       </c>
-      <c r="W37" s="11" t="n">
-        <v>7</v>
+      <c r="W37" s="14" t="n">
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3645,10 +3653,10 @@
       <c r="C38" s="3" t="n">
         <v>443.3</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="14" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="14" t="n">
         <v>13.9</v>
       </c>
       <c r="F38" s="8" t="n">
@@ -3666,7 +3674,9 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
@@ -3685,7 +3695,7 @@
       <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3697,10 +3707,10 @@
       <c r="U38" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="14" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="11" t="n">
+      <c r="W38" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3811,7 +3821,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>17.1</v>
+        <v>617.1</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>30.7</v>
@@ -3838,19 +3848,19 @@
         <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>9.1</v>
+        <v>12.6</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>51</v>
+        <v>68.5</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="Q40" s="8" t="n">
         <v>30</v>
@@ -3899,13 +3909,13 @@
         <v>587.5</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>15.2</v>
@@ -3923,19 +3933,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>7.4</v>
+        <v>11.9</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>10.3</v>
+        <v>13.9</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>49</v>
+        <v>67.5</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q41" s="8" t="n">
         <v>29.8</v>
@@ -4040,11 +4050,11 @@
       <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>23</v>
+      <c r="W42" s="16" t="n">
+        <v>12.3</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4069,13 +4079,13 @@
         <v>554</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>14.1</v>
@@ -4090,7 +4100,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>17.7</v>
@@ -4125,7 +4135,7 @@
       <c r="V43" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W43" s="15" t="n">
+      <c r="W43" s="16" t="n">
         <v>4.5</v>
       </c>
       <c r="X43" s="8" t="n">
@@ -4154,10 +4164,10 @@
         <v>258</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>22.9</v>
@@ -4175,7 +4185,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>16.6</v>
@@ -4195,16 +4205,16 @@
       <c r="Q44" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
+      <c r="R44" s="8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S44" s="8" t="n">
         <v>7.8</v>
       </c>
-      <c r="T44" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="U44" s="3" t="n">
+      <c r="T44" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="U44" s="8" t="n">
         <v>32.8</v>
       </c>
       <c r="V44" s="8" t="n">
@@ -4236,13 +4246,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>312.2</v>
+        <v>3312.2</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>183.8</v>
+        <v>183.7</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>137.9</v>
@@ -4257,19 +4267,19 @@
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K45" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="K45" s="14" t="n">
         <v>12.2</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>100.3</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>55.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>2.7</v>
+        <v>27</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4280,7 +4290,7 @@
       <c r="Q45" s="8" t="n">
         <v>173</v>
       </c>
-      <c r="R45" s="13" t="inlineStr"/>
+      <c r="R45" s="17" t="inlineStr"/>
       <c r="S45" s="3" t="n">
         <v>23.8</v>
       </c>
@@ -4293,11 +4303,11 @@
       <c r="V45" s="8" t="n">
         <v>144.2</v>
       </c>
-      <c r="W45" s="11" t="n">
-        <v>22.8</v>
+      <c r="W45" s="14" t="n">
+        <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>54.7</v>
+        <v>186.2</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4318,16 +4328,16 @@
         <v>551.8</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>20.6</v>
+        <v>30.6</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>15.3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>12.3</v>
+        <v>23</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>15.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
@@ -4374,14 +4384,14 @@
       <c r="V46" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W46" s="11" t="n">
-        <v>14.4</v>
+      <c r="W46" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>27.1</v>
+        <v>31.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -1345,7 +1345,7 @@
         <v>27.9</v>
       </c>
       <c r="W10" s="14" t="n">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
@@ -1373,15 +1373,15 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>31.1</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>10.4</v>
@@ -1746,10 +1746,10 @@
         <v>12.6</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>31</v>
@@ -1816,13 +1816,13 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>52.1</v>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>515.4</v>
+        <v>55.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>23.6</v>
@@ -1904,7 +1904,7 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>18</v>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>352.1</v>
+        <v>552.1</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.9</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>20.5</v>
@@ -2051,10 +2051,10 @@
         <v>526.4</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>22.9</v>
@@ -2107,17 +2107,17 @@
       <c r="V19" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="16" t="n">
-        <v>1.3</v>
+      <c r="W19" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>6.7</v>
+        <v>14.9</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>19</v>
+        <v>41.9</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>28.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2136,15 +2136,15 @@
         <v>322.5</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>31.4</v>
+        <v>23.4</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G20" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2224,10 +2224,10 @@
         <v>30.9</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>14.5</v>
@@ -2391,25 +2391,25 @@
         <v>2547.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>158.4</v>
+        <v>150.5</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="G23" s="8" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>22.2</v>
+        <v>69</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
+        <v>57.2</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>3.3</v>
@@ -2421,10 +2421,10 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>41.3</v>
@@ -2600,7 +2600,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2652,10 +2652,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2828,7 +2828,7 @@
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>20.4</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2854,20 +2854,20 @@
       <c r="P28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S28" s="3" t="n">
+      <c r="R28" s="16" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="S28" s="8" t="n">
         <v>4.5</v>
       </c>
-      <c r="T28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>13.4</v>
+      <c r="T28" s="8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>43.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>271.9</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>161.6</v>
@@ -2991,7 +2991,7 @@
       <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="8" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="8" t="n">
@@ -3004,7 +3004,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="8" t="n">
         <v>10.9</v>
@@ -3037,7 +3037,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>19.4</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.7</v>
@@ -3112,7 +3112,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3133,7 +3133,7 @@
         <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>611.1</v>
+        <v>61.1</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>33.8</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>243.7</v>
+        <v>43.7</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>31.3</v>
@@ -3296,7 +3296,7 @@
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>22.2</v>
+        <v>42.2</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>13.9</v>
@@ -3384,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0.2</v>
+        <v>33.2</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>19.2</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>341.3</v>
+        <v>34.1</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>25.4</v>
@@ -3549,7 +3549,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>20.2</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2216.6</v>
+        <v>221.6</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>151.6</v>
@@ -3583,7 +3583,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3628,7 +3628,7 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="14" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3674,9 +3674,7 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
@@ -3748,7 +3746,7 @@
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>11.2</v>
@@ -3848,33 +3846,33 @@
         <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>10.4</v>
+        <v>5.6</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>12.6</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>68.5</v>
+        <v>51</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q40" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S40" s="3" t="n">
+      <c r="R40" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S40" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="T40" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="T40" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U40" s="8" t="n">
         <v>34.2</v>
       </c>
       <c r="V40" s="8" t="n">
@@ -3933,19 +3931,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>13.9</v>
+        <v>10.3</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>67.5</v>
+        <v>49</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>6.7</v>
+        <v>10.8</v>
       </c>
       <c r="Q41" s="8" t="n">
         <v>29.8</v>
@@ -3965,16 +3963,16 @@
       <c r="V41" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="Y41" s="3" t="n">
+      <c r="W41" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y41" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="Z41" s="3" t="n">
+      <c r="Z41" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -4051,10 +4049,10 @@
         <v>19</v>
       </c>
       <c r="W42" s="16" t="n">
-        <v>12.3</v>
+        <v>81.3</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4161,7 +4159,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
+        <v>58</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>30.7</v>
@@ -4205,31 +4203,31 @@
       <c r="Q44" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S44" s="8" t="n">
+      <c r="R44" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="T44" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="U44" s="8" t="n">
+      <c r="T44" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="V44" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Y44" s="8" t="n">
+      <c r="W44" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y44" s="3" t="n">
         <v>50.8</v>
       </c>
-      <c r="Z44" s="8" t="n">
+      <c r="Z44" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -4246,7 +4244,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3312.2</v>
+        <v>331.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>183.7</v>
@@ -4261,13 +4259,13 @@
         <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>32.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="14" t="n">
         <v>12.2</v>
@@ -4275,11 +4273,11 @@
       <c r="L45" s="8" t="n">
         <v>100.3</v>
       </c>
-      <c r="M45" s="8" t="n">
-        <v>65.09999999999999</v>
+      <c r="M45" s="14" t="n">
+        <v>65</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27</v>
+        <v>57.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4298,7 +4296,7 @@
         <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>182.6</v>
+        <v>185.6</v>
       </c>
       <c r="V45" s="8" t="n">
         <v>144.2</v>
@@ -4307,7 +4305,7 @@
         <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>186.2</v>
+        <v>64.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4349,12 +4347,12 @@
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="8" t="n">
@@ -4385,13 +4383,13 @@
         <v>24</v>
       </c>
       <c r="W46" s="14" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>31.1</v>
+        <v>21.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,19 +161,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -820,13 +814,13 @@
         <v>4.6</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>64.2</v>
+        <v>31.1</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>4.7</v>
+        <v>9.1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33.3</v>
@@ -835,13 +829,13 @@
         <v>13.7</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>15.7</v>
+        <v>2.4</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>30.6</v>
+        <v>4.6</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>35.5</v>
+        <v>48.9</v>
       </c>
       <c r="V4" s="11" t="inlineStr"/>
       <c r="W4" s="11" t="inlineStr"/>
@@ -895,13 +889,13 @@
         <v>5.5</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>63.6</v>
+        <v>31.8</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>5.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>31.7</v>
@@ -910,19 +904,19 @@
         <v>14</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>34.1</v>
+        <v>8.4</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>30.8</v>
+        <v>42.8</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="16" t="n">
-        <v>0.9</v>
+      <c r="W5" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="X5" s="8" t="n">
         <v>6.5</v>
@@ -980,13 +974,13 @@
         <v>6</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>65.8</v>
+        <v>36.4</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>32.7</v>
@@ -995,19 +989,19 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>17.3</v>
+        <v>5.4</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>34.9</v>
+        <v>10.8</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>32.3</v>
+        <v>44.2</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="16" t="n">
-        <v>3.9</v>
+      <c r="W6" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="X6" s="8" t="n">
         <v>8.1</v>
@@ -1065,13 +1059,13 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>9.1</v>
+        <v>4.4</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>62.8</v>
+        <v>30.7</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>34.7</v>
@@ -1080,19 +1074,19 @@
         <v>13.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>15.8</v>
+        <v>1.6</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>28.5</v>
+        <v>2.8</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>39.6</v>
+        <v>53.8</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="W7" s="16" t="n">
-        <v>0.9</v>
+      <c r="W7" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>6.5</v>
@@ -1150,13 +1144,13 @@
         <v>10.8</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>12.9</v>
+        <v>7.3</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>58.6</v>
+        <v>33.1</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>32.6</v>
@@ -1165,13 +1159,13 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>17.2</v>
+        <v>5.2</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>34.8</v>
+        <v>10.7</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>32.1</v>
+        <v>44</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
@@ -1213,7 +1207,7 @@
       <c r="F9" s="8" t="n">
         <v>111.4</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="15" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1318,13 +1312,13 @@
         <v>6.5</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>63</v>
+        <v>32.7</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>5.7</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>33</v>
@@ -1333,13 +1327,13 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>16.4</v>
+        <v>3.7</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>32.6</v>
+        <v>7.4</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>34</v>
+        <v>46.6</v>
       </c>
       <c r="V10" s="14" t="n">
         <v>27.9</v>
@@ -1403,19 +1397,19 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>11.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>5.7</v>
+      <c r="R11" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1433,13 +1427,13 @@
         <v>14.5</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>16.5</v>
+        <v>11.6</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>63.6</v>
+        <v>44.7</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1488,19 +1482,19 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>69</v>
+        <v>50.5</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <v>0.9</v>
+      <c r="R12" s="15" t="n">
+        <v>4.4</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>6.5</v>
@@ -1515,7 +1509,7 @@
         <v>21.8</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>10</v>
+        <v>15.1</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>12.3</v>
@@ -1573,19 +1567,19 @@
         <v>10.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>12.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>67.7</v>
+        <v>46.2</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>1.7</v>
+      <c r="R13" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>6.9</v>
@@ -1600,7 +1594,7 @@
         <v>27</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>7.3</v>
+        <v>15.1</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>10.2</v>
@@ -1658,19 +1652,19 @@
         <v>12</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>59.6</v>
+        <v>36.2</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>2.5</v>
+      <c r="R14" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>7.3</v>
@@ -1688,13 +1682,13 @@
         <v>14.5</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>46.3</v>
+        <v>22.4</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>19.2</v>
+        <v>27.7</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1743,19 +1737,19 @@
         <v>10.4</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>67.2</v>
+        <v>45.2</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>6.2</v>
+        <v>10.3</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>1.7</v>
+      <c r="R15" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>6.9</v>
@@ -1773,13 +1767,13 @@
         <v>14</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>16</v>
+        <v>7.1</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>44.5</v>
+        <v>19.7</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>19.9</v>
+        <v>28.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1839,8 +1833,8 @@
       <c r="Q16" s="8" t="n">
         <v>154.7</v>
       </c>
-      <c r="R16" s="8" t="n">
-        <v>12.5</v>
+      <c r="R16" s="14" t="n">
+        <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
@@ -1855,7 +1849,7 @@
         <v>131.3</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>60.3</v>
+        <v>73.2</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
@@ -1913,19 +1907,19 @@
         <v>10.4</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>12.6</v>
+        <v>7.5</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>61.1</v>
+        <v>36.2</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>8</v>
+        <v>13.2</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <v>2.5</v>
+      <c r="R17" s="14" t="n">
+        <v>14.7</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>7.3</v>
@@ -1943,13 +1937,13 @@
         <v>14.5</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>48.2</v>
+        <v>24.8</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>17.7</v>
+        <v>25.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1996,19 +1990,19 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>67.5</v>
+        <v>41.7</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>2.7</v>
+      <c r="R18" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>7.4</v>
@@ -2022,8 +2016,8 @@
       <c r="V18" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="16" t="n">
-        <v>4.5</v>
+      <c r="W18" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="8" t="n">
         <v>8.4</v>
@@ -2081,19 +2075,19 @@
         <v>7.9</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>68.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="8" t="n">
-        <v>-0</v>
+      <c r="R19" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>6.1</v>
@@ -2111,13 +2105,13 @@
         <v>12.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>14.9</v>
+        <v>5.4</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>41.9</v>
+        <v>15.1</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>20.6</v>
+        <v>30.1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2166,19 +2160,19 @@
         <v>12.6</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>70.7</v>
+        <v>52.9</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>5</v>
+      <c r="R20" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>8.699999999999999</v>
@@ -2196,13 +2190,13 @@
         <v>12.4</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>14.4</v>
+        <v>7.7</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>53.8</v>
+        <v>28.9</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>12.4</v>
+        <v>19</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2251,19 +2245,19 @@
         <v>11.5</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>13.6</v>
+        <v>9.4</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>67</v>
+        <v>46.2</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>6.7</v>
+        <v>10.9</v>
       </c>
       <c r="Q21" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="8" t="n">
-        <v>3</v>
+      <c r="R21" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>7.6</v>
@@ -2281,13 +2275,13 @@
         <v>14.5</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>48.2</v>
+        <v>24.8</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>17.7</v>
+        <v>25.7</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2336,19 +2330,19 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>69</v>
+        <v>48.3</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q22" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="8" t="n">
-        <v>1.5</v>
+      <c r="R22" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>6.8</v>
@@ -2366,13 +2360,13 @@
         <v>14.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>16.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>46.6</v>
+        <v>22.9</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>19.1</v>
+        <v>27.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2432,9 +2426,7 @@
       <c r="Q23" s="8" t="n">
         <v>154.4</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="R23" s="13" t="inlineStr"/>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
@@ -2447,7 +2439,7 @@
       <c r="V23" s="8" t="n">
         <v>130.5</v>
       </c>
-      <c r="W23" s="14" t="n">
+      <c r="W23" s="8" t="n">
         <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2506,19 +2498,19 @@
         <v>10.1</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>12.4</v>
+        <v>8.5</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>68.90000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q24" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R24" s="8" t="n">
-        <v>2.4</v>
+      <c r="R24" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
@@ -2532,17 +2524,17 @@
       <c r="V24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="14" t="n">
+      <c r="W24" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>15.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>46.6</v>
+        <v>21.9</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>18</v>
+        <v>26.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2591,15 +2583,15 @@
         <v>11.8</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>13.8</v>
+        <v>8.4</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>59.9</v>
+        <v>36.4</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q25" s="16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Q25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
@@ -2676,19 +2668,19 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12.7</v>
+        <v>9</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>70.3</v>
+        <v>50</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="16" t="n">
-        <v>2.7</v>
+      <c r="R26" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="S26" s="8" t="n">
         <v>7.4</v>
@@ -2761,19 +2753,19 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>12.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>69.90000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q27" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="16" t="n">
-        <v>2.1</v>
+      <c r="R27" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S27" s="8" t="n">
         <v>7.1</v>
@@ -2787,8 +2779,8 @@
       <c r="V27" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W27" s="8" t="n">
-        <v>6.4</v>
+      <c r="W27" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="X27" s="8" t="n">
         <v>9.6</v>
@@ -2843,7 +2835,7 @@
         <v>16.5</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="N28" s="8" t="n">
         <v>8.800000000000001</v>
@@ -2857,8 +2849,8 @@
       <c r="Q28" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R28" s="16" t="n">
-        <v>-4.1</v>
+      <c r="R28" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>4.5</v>
@@ -2931,19 +2923,19 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>10.2</v>
+        <v>5.9</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>65.3</v>
+        <v>37.7</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q29" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="16" t="n">
-        <v>-3.9</v>
+      <c r="R29" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>4.6</v>
@@ -2957,8 +2949,8 @@
       <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="16" t="n">
-        <v>1.7</v>
+      <c r="W29" s="15" t="n">
+        <v>3.3</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>6.9</v>
@@ -3012,7 +3004,7 @@
       <c r="L30" s="8" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="14" t="n">
+      <c r="M30" s="8" t="n">
         <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3093,17 +3085,17 @@
       <c r="L31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="14" t="n">
+      <c r="M31" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>12.4</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>66.3</v>
+        <v>43.4</v>
       </c>
       <c r="P31" s="8" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="Q31" s="14" t="n">
         <v>31</v>
@@ -3180,13 +3172,13 @@
         <v>5.7</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>65.3</v>
+        <v>35.1</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q32" s="8" t="n">
         <v>33.6</v>
@@ -3195,13 +3187,13 @@
         <v>14.1</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>16.1</v>
+        <v>2.8</v>
       </c>
       <c r="T32" s="8" t="n">
-        <v>30.9</v>
+        <v>5.4</v>
       </c>
       <c r="U32" s="8" t="n">
-        <v>36</v>
+        <v>49.3</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>9</v>
@@ -3263,13 +3255,13 @@
         <v>11.2</v>
       </c>
       <c r="N33" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="P33" s="8" t="n">
         <v>13.3</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>8.300000000000001</v>
       </c>
       <c r="Q33" s="8" t="n">
         <v>26</v>
@@ -3278,13 +3270,13 @@
         <v>14.7</v>
       </c>
       <c r="S33" s="8" t="n">
-        <v>16.7</v>
+        <v>9</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>49.7</v>
+        <v>26.9</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>16.9</v>
+        <v>24.6</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3348,13 +3340,13 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>68.7</v>
+        <v>48.7</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q34" s="8" t="n">
         <v>19</v>
@@ -3363,13 +3355,13 @@
         <v>13.4</v>
       </c>
       <c r="S34" s="8" t="n">
-        <v>15.4</v>
+        <v>11.6</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>70</v>
+        <v>52.6</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>6.6</v>
+        <v>10.4</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>19</v>
@@ -3433,19 +3425,19 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>14.6</v>
+        <v>10.8</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>69.8</v>
+        <v>51.6</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>6.3</v>
+        <v>10.1</v>
       </c>
       <c r="Q35" s="8" t="n">
         <v>30.3</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>6.7</v>
+        <v>15.9</v>
       </c>
       <c r="S35" s="8" t="n">
         <v>9.800000000000001</v>
@@ -3516,19 +3508,19 @@
         <v>12.3</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>70.2</v>
+        <v>51.9</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>6.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="S36" s="8" t="n">
         <v>10.7</v>
@@ -3612,7 +3604,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.5</v>
       </c>
-      <c r="R37" s="14" t="n">
+      <c r="R37" s="8" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3682,28 +3674,28 @@
         <v>10.6</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>12.8</v>
+        <v>8.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>66.8</v>
+        <v>44.9</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="14" t="n">
+      <c r="R38" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>47.1</v>
+        <v>23.4</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>18.5</v>
+        <v>26.8</v>
       </c>
       <c r="V38" s="14" t="n">
         <v>22.8</v>
@@ -3767,19 +3759,19 @@
         <v>10.2</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>12.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>73</v>
+        <v>53.9</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>4.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q39" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="R39" s="8" t="n">
-        <v>7</v>
+      <c r="R39" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S39" s="8" t="n">
         <v>10</v>
@@ -3849,7 +3841,7 @@
         <v>15.8</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="8" t="n">
         <v>9.1</v>
@@ -3863,8 +3855,8 @@
       <c r="Q40" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="8" t="n">
-        <v>4.3</v>
+      <c r="R40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>8.300000000000001</v>
@@ -3878,8 +3870,8 @@
       <c r="V40" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>7.1</v>
+      <c r="W40" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="X40" s="8" t="n">
         <v>10.1</v>
@@ -3934,7 +3926,7 @@
         <v>18.4</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>7.4</v>
+        <v>11.9</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>10.3</v>
@@ -3948,8 +3940,8 @@
       <c r="Q41" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>5.9</v>
+      <c r="R41" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S41" s="8" t="n">
         <v>9.300000000000001</v>
@@ -3963,8 +3955,8 @@
       <c r="V41" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W41" s="8" t="n">
-        <v>7.6</v>
+      <c r="W41" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="X41" s="8" t="n">
         <v>10.4</v>
@@ -4022,19 +4014,19 @@
         <v>10.9</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>68.2</v>
+        <v>47.3</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q42" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <v>6.8</v>
+      <c r="R42" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S42" s="8" t="n">
         <v>9.9</v>
@@ -4048,7 +4040,7 @@
       <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W42" s="16" t="n">
+      <c r="W42" s="15" t="n">
         <v>81.3</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4107,13 +4099,13 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>68.8</v>
+        <v>49.4</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>6.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q43" s="8" t="n">
         <v>28.9</v>
@@ -4133,8 +4125,8 @@
       <c r="V43" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W43" s="16" t="n">
-        <v>4.5</v>
+      <c r="W43" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X43" s="8" t="n">
         <v>8.4</v>
@@ -4192,13 +4184,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>64.09999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>6.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q44" s="8" t="n">
         <v>29.2</v>
@@ -4273,7 +4265,7 @@
       <c r="L45" s="8" t="n">
         <v>100.3</v>
       </c>
-      <c r="M45" s="14" t="n">
+      <c r="M45" s="8" t="n">
         <v>65</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4288,7 +4280,7 @@
       <c r="Q45" s="8" t="n">
         <v>173</v>
       </c>
-      <c r="R45" s="17" t="inlineStr"/>
+      <c r="R45" s="13" t="inlineStr"/>
       <c r="S45" s="3" t="n">
         <v>23.8</v>
       </c>
@@ -4352,23 +4344,23 @@
       <c r="L46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="14" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>67.7</v>
+        <v>46.5</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>5.5</v>
+      <c r="R46" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="S46" s="8" t="n">
         <v>9</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/501/501_197210_SF.JPG_post_QA_QC.xlsx
@@ -1212,7 +1212,7 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1376,7 +1376,7 @@
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="13" t="n"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="J16" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2372,7 +2372,7 @@
       <c r="J23" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>16.1</v>
       </c>
       <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
+      <c r="K25" s="13" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="J27" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="13" t="n"/>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="J30" s="3" t="n">
         <v>35.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>81.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3529,7 +3529,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="10" t="n"/>
       <c r="L37" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="J39" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="K39" s="3" t="n"/>
+      <c r="K39" s="13" t="n"/>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="J45" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
